--- a/Data/Sylogism.xlsx
+++ b/Data/Sylogism.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are living beings. Are all cats living beings?</t>
+          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,62 +501,62 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>If all cats are animals and all animals are living beings, all cats are living beings.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some birds are flying creatures. All flying creatures can fly. Can some birds fly?</t>
+          <t>All stones are rocks. Some rocks are heavy. Conclusions: I. Some stones are heavy. II. All heavy are rocks.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Some birds belong to flying creatures which can fly.</t>
+          <t>Overlap is not definite.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>No dogs are cats. All cats are animals. Are no dogs animals?</t>
+          <t>All flowers are beautiful. Some beautiful things are expensive. Are some flowers expensive?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>We cannot conclude about dogs being animals.</t>
+          <t>No direct info about flowers and expensive.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>All pens are tools. Some tools are pencils. Are some pens pencils?</t>
+          <t>Some engineers are scientists. No scientist is artist. Are some engineers not artists?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No direct relation between pens and pencils.</t>
+          <t>Engineers partly overlap scientists; scientists exclude artists.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Some fruits are sweet. All sweets are tasty. Are some fruits tasty?</t>
+          <t>All actors are dancers. Some dancers are singers. Can we conclude some actors are singers?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -661,182 +661,182 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Some fruits are sweet and sweets are tasty.</t>
+          <t>Partial overlap between dancers and singers; actors may or may not be singers.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>No flowers are trees. Some trees are plants. Are some flowers plants?</t>
+          <t>No pen is marker. All markers are tools. Conclusions: I. Some pens are not tools. II. No marker is pen.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No direct relation given between flowers and plants.</t>
+          <t>Negative statement from given facts.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>All cars are vehicles. Some vehicles are fast. Are all cars fast?</t>
+          <t>All men are humans. Some humans are kind. Conclusions: I. Some men are kind. II. All men are kind.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Only some vehicles are fast, no info about cars.</t>
+          <t>Some does not apply across unless proven.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Some boys are students. All students study. Do some boys study?</t>
+          <t>No bird is mammal. All mammals are warm-blooded. Conclusions: I. No bird is warm-blooded. II. Some warm-blooded are mammals.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Some boys belong to students who study.</t>
+          <t>All mammals ⊂ warm-blooded, so II true.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>No pencils are erasers. All erasers are stationery. Are no pencils stationery?</t>
+          <t>Some teachers are doctors. All doctors are professionals. Conclusions: I. Some teachers are professionals. II. All professionals are doctors.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No info on pencils and stationery relation.</t>
+          <t>Partial link via doctors.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>All flowers are beautiful. Some beautiful things are expensive. Are some flowers expensive?</t>
+          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -861,102 +861,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No direct info about flowers and expensive.</t>
+          <t>No R is S, so some P not S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Some books are novels. All novels are stories. Are some books stories?</t>
+          <t>Some apples are fruits. All fruits are juicy. Conclusions: I. Some apples are juicy. II. All juicy things are fruits.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Some books belong to novels which are stories.</t>
+          <t>Partial overlap with juicy items.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>No cars are bikes. All bikes are fast. Are no cars fast?</t>
+          <t>Some books are pens. Some pens are colors. Conclusions: I. Some books are colors. II. All colors are pens.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No info on cars and fast relation.</t>
+          <t>Indirect link not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>All rivers are water bodies. Some water bodies are dirty. Are some rivers dirty?</t>
+          <t>No cars are bikes. All bikes are fast. Are no cars fast?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No direct info on rivers and dirty.</t>
+          <t>No info on cars and fast relation.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Some men are doctors. All doctors help people. Do some men help people?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Some men are doctors who help people.</t>
+          <t>Because some Z not X, some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>No birds are mammals. All mammals breathe air. Are no birds breathe air?</t>
+          <t>No S is T. Some T are U. All U are V. Are some S not V?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1061,62 +1061,62 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No info on birds and breathing.</t>
+          <t>No S is T, so some S not V.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are red. Are some apples red?</t>
+          <t>All lions are wild. No wild is pet. Conclusions: I. No lion is pet. II. Some lions are pets.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No direct info on apples and red.</t>
+          <t>Categorical exclusion carries to subset.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Some students are intelligent. All intelligent people succeed. Do some students succeed?</t>
+          <t>All lions are animals. Some animals are wild. Are all lions wild?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1141,37 +1141,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Some students are intelligent who succeed.</t>
+          <t>Only some animals are wild.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>No fish are birds. All birds have wings. Are no fish have wings?</t>
+          <t>No lion is a deer. Some deer are animals. Conclusion?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No lion is an animal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some lions are deer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No deer is lion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No deer is lion</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No info on fish and wings.</t>
+          <t>No lion → deer = No deer → lion</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>All pens are useful. Some useful things are costly. Are some pens costly?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1226,57 +1226,57 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No direct info on pens and costly.</t>
+          <t>No conclusion.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Some trees are tall. All tall things cast shadows. Are some trees casting shadows?</t>
+          <t>No bird is insect. All parrots are birds. Conclusions: I. No parrot is insect. II. Some insects are birds.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Some trees are tall and tall things cast shadows.</t>
+          <t>Parrot subset inherits bird restriction.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>No chairs are tables. All tables are furniture. Are no chairs furniture?</t>
+          <t>All cars are vehicles. Some vehicles are fast. Are all cars fast?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No info about chairs and furniture.</t>
+          <t>Only some vehicles are fast, no info about cars.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>All birds can fly. Some birds are colorful. Are some colorful things flying?</t>
+          <t>Some books are novels. All novels are stories. Are some books stories?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1341,37 +1341,37 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No direct info on colorful things and flying.</t>
+          <t>Some books belong to novels which are stories.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Some cars are red. All red things are bright. Are some cars bright?</t>
+          <t>Some boys are students. All students are intelligent. What follows?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All boys are intelligent</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some boys are intelligent</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All intelligent are students</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1381,62 +1381,62 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some boys are intelligent</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Some cars are red and red things are bright.</t>
+          <t>Some boys → students → intelligent</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>No books are papers. All papers are white. Are no books white?</t>
+          <t>All dogs are loyal. No loyal being is dishonest. Conclusions: I. No dog is dishonest. II. All dishonest are dogs.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No info on books and white.</t>
+          <t>No and "All" combined can show exclusivity.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Some students are hardworking. All hardworking people achieve success. Do some students achieve success?</t>
+          <t>No A is B. All B are C. Some C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1461,22 +1461,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Some students are hardworking who achieve success.</t>
+          <t>No direct link between A and D.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>All actors are dancers. Some dancers are singers. Can we conclude some actors are singers?</t>
+          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1506,57 +1506,57 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Partial overlap between dancers and singers; actors may or may not be singers.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>No doctors are lawyers. Some lawyers are teachers. Are some doctors teachers?</t>
+          <t>Some apples are fruits. All fruits are healthy. Conclusions: I. Some apples are healthy. II. All apples are healthy.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No direct relation between doctors and teachers.</t>
+          <t>Part of a group being linked to another through common element.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>All cars are vehicles. Some vehicles are expensive. Are all cars expensive?</t>
+          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1581,62 +1581,62 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Some vehicles are expensive, cars may or may not be expensive.</t>
+          <t>No L is M, so some J not M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Some fruits are apples. All apples are red. Are some fruits red?</t>
+          <t>All apples are fruits. Some fruits are sweet. What follows?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some apples are sweet</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All sweet are fruits</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some fruits are apples</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>All apples are sweet</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some fruits are apples</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>If some fruits are apples and apples are red, some fruits are red.</t>
+          <t>All apples → fruits, so some fruits ← apples</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>No cats are dogs. All dogs are animals. Are no cats animals?</t>
+          <t>All mountains are high. Some high places are cold. Are all mountains cold?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1666,72 +1666,72 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>No info on cats and animals.</t>
+          <t>Partial overlap between high and cold places.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>All roses are flowers. Some flowers are fragrant. Are all roses fragrant?</t>
+          <t>All squares are rectangles. All rectangles are shapes. Conclusions: I. All squares are shapes. II. Some shapes are squares.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Only some flowers are fragrant, no info if roses are.</t>
+          <t>Multiple logical links proven.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Some engineers are scientists. No scientist is artist. Are some engineers not artists?</t>
+          <t>No fish is bird. All birds can fly. Conclusion?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No fish can fly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All fish are birds</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some fish can fly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1741,22 +1741,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No fish can fly</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Engineers partly overlap scientists; scientists exclude artists.</t>
+          <t>No fish → bird → fly</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>All mountains are high. Some high places are cold. Are all mountains cold?</t>
+          <t>All cars are vehicles. Some vehicles are expensive. Are all cars expensive?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1786,32 +1786,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Partial overlap between high and cold places.</t>
+          <t>Some vehicles are expensive, cars may or may not be expensive.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>No bats are birds. All birds can fly. Are no bats able to fly?</t>
+          <t>No table is chair. All chairs are wooden. Conclusion?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some tables are wooden</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No table is wooden</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No chair is table</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1821,22 +1821,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No chair is table</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>No info on bats' flying ability here.</t>
+          <t>No table → chair = No chair → table</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Some boys are tall. All tall people are strong. Are some boys strong?</t>
+          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1861,37 +1861,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Some boys are tall and tall people are strong.</t>
+          <t>No conclusive info.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>No cars are bicycles. Some bicycles are two-wheelers. Are no cars two-wheelers?</t>
+          <t>Some toys are plastic. All plastic is harmful. Conclusion?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some toys are harmful</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All toys are harmful</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some harmful are toys</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1901,22 +1901,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some toys are harmful</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>No info on cars and two-wheelers.</t>
+          <t>Some toys → plastic → harmful</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>All students are learners. Some learners are athletes. Are some students athletes?</t>
+          <t>All apples are fruits. Some fruits are sour. Are some apples sour?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>No direct info on students and athletes.</t>
+          <t>No info on apples being sour.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Some doctors are rich. All rich people are happy. Are some doctors happy?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1981,62 +1981,62 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Some doctors are rich and rich people are happy.</t>
+          <t>No direct conclusion can be drawn about A and D.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>No cats are mice. All mice are small. Are no cats small?</t>
+          <t>All cars are vehicles. All trucks are vehicles. Conclusions: I. Some trucks are cars. II. All cars are trucks.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>No info on cats and small.</t>
+          <t>Common class doesn’t mean crossover between groups.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>All flowers are plants. Some plants are medicinal. Are all flowers medicinal?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Only some plants are medicinal.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Some cars are fast. All fast things are expensive. Are some cars expensive?</t>
+          <t>No books are papers. All papers are white. Are no books white?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2101,117 +2101,117 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Some cars are fast and fast things are expensive.</t>
+          <t>No info on books and white.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>No students are lazy. Some lazy people are careless. Are no students careless?</t>
+          <t>All kids are students. No student is teacher. Conclusions: I. No kid is teacher. II. Some teachers are students.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>No info on students and careless.</t>
+          <t>Exclusion travels to subgroup.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>All birds have feathers. Some birds are colorful. Are some colorful things having feathers?</t>
+          <t>All apples are fruits. No fruit is vegetable. Conclusions: I. No apple is vegetable. II. Some apples are vegetables.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>No direct info on colorful things and feathers.</t>
+          <t>Exclusive property holds.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Some men are honest. All honest people are respected. Are some men respected?</t>
+          <t>All bats are mammals. Some mammals are nocturnal. Conclusion?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some bats are nocturnal</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All bats are nocturnal</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some mammals are bats</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2221,62 +2221,62 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some mammals are bats</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Some men are honest and honest people are respected.</t>
+          <t>All bats → mammals</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>No dogs are cats. All cats are pets. Are no dogs pets?</t>
+          <t>Some mangoes are sweet. All sweet things are healthy. Conclusions: I. Some mangoes are healthy. II. All mangoes are healthy.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>No info on dogs and pets.</t>
+          <t>Indirect conclusion from overlap.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are sour. Are some apples sour?</t>
+          <t>Some cars are red. All red things are bright. Are some cars bright?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2301,62 +2301,62 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>No info on apples being sour.</t>
+          <t>Some cars are red and red things are bright.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Some flowers are red. All red things are attractive. Are some flowers attractive?</t>
+          <t>All windows are doors. Some doors are walls. Conclusions: I. Some windows are walls. II. Some doors are windows.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Some flowers are red and red things are attractive.</t>
+          <t>Some doors are windows due to inclusion.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>No books are newspapers. Some newspapers are daily. Are no books daily?</t>
+          <t>No S is R. Some R are Q. All Q are P. Are some P not S?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2381,62 +2381,62 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>No info on books being daily.</t>
+          <t>Since no S is R, some P which are Q and R are not S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>All lions are animals. Some animals are wild. Are all lions wild?</t>
+          <t>All lions are animals. No animal is plant. Conclusions: I. No lion is plant. II. All lions are plants.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Only some animals are wild.</t>
+          <t>Lions ⊂ animals, animals ≠ plants.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Some teachers are strict. All strict people are effective. Are some teachers effective?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2466,57 +2466,57 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Some teachers are strict and strict people are effective.</t>
+          <t>Because some Z not X, some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>All A are B. Some C are not B. Can some C be A?</t>
+          <t>No chair is desk. Some desks are tables. Conclusions: I. No chair is table. II. Some tables are not chairs.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Since some C are not B, some C might or might not be A.</t>
+          <t>Partial exclusion inferred.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>No X is Y. All Y are Z. Are some Z not X?</t>
+          <t>No D is E. Some F are D. All F are G. Are some G not E?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Since no X is Y and all Y are Z, some Z are not X.</t>
+          <t>Since no D is E and some F are D, some G (which include F) are not E.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Some P are Q. No Q is R. Are some P not R?</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2586,133 +2586,133 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Since no Q is R, some P may not be R.</t>
+          <t>Since no V is W, some T which are U and U are V, are not W.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>All M are N. Some N are O. No O is P. Are some M not P?</t>
+          <t>All fruits are healthy. Some healthy are tasty. Conclusion?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some fruits are tasty</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All healthy are fruits</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some fruits are healthy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>All tasty are fruits</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some fruits are healthy</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Some M could belong to N which belong to O; none O is P, so some M are not P.</t>
+          <t>All fruits → healthy</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>No D is E. Some F are D. All F are G. Are some G not E?</t>
+          <t>All roses are flowers. Some flowers are red. Conclusions: I. Some roses are red. II. All red things are flowers.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Since no D is E and some F are D, some G (which include F) are not E.</t>
+          <t>Overlap cannot be confirmed.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
+          <t>All cows are animals. All animals are herbivores. Conclusions: I. Some cows are herbivores. II. All cows are herbivores.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Since no L is M and some L are K, some J may not be M.</t>
+          <t>Cows ⊂ animals ⊂ herbivores.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2746,17 +2746,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Since no V is W, some T which are U and U are V, are not W.</t>
+          <t>No V is W, so some T are not W.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>No S is R. Some R are Q. All Q are P. Are some P not S?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2781,102 +2781,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Since no S is R, some P which are Q and R are not S.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All paper is white. Some white is light. Conclusions: I. Some paper is light. II. All light is white.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Because some Z are not X, and some Y are Z, some Y may not be X.</t>
+          <t>No guaranteed overlap shown.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>Some keys are locks. Some locks are doors. Conclusions: I. Some keys are doors. II. All keys are doors.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>No direct conclusion can be drawn about A and D.</t>
+          <t>No definite connection between keys and doors.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>No conclusive relation between M and P.</t>
+          <t>No conclusive data.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>No F is G. All G are H. Some H are I. Are some F not I?</t>
+          <t>No P is Q. All Q are R. Some R are S. Are some P not S?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>No direct info on F and I.</t>
+          <t>Cannot conclude about P and S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Some K are L. Some L are M. No M is N. Are some K not N?</t>
+          <t>All pens are useful. Some useful things are costly. Are some pens costly?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>No direct info on pens and costly.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3021,22 +3021,22 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Because no Z is W, and some Y are Z, some X may not be W.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>No P is Q. All Q are R. Some R are S. Are some P not S?</t>
+          <t>All pens are tools. Some tools are pencils. Are some pens pencils?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3066,32 +3066,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cannot conclude about P and S.</t>
+          <t>No direct relation between pens and pencils.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
+          <t>Some pencils are long. All long things are thin. Conclusion?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some pencils are thin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All pencils are thin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some thin things are pencils</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3101,22 +3101,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some pencils are thin</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some pencils → long → thin</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>No birds are mammals. All mammals breathe air. Are no birds breathe air?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>No conclusive relation.</t>
+          <t>No info on birds and breathing.</t>
         </is>
       </c>
     </row>
@@ -3156,22 +3156,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>All mangoes are fruits. No fruit is vegetable. Conclusion?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some mangoes are vegetables</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All mangoes are vegetables</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No mango is vegetable</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3181,37 +3181,37 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No mango is vegetable</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>No conclusion.</t>
+          <t>All mangoes → fruits, and no fruit → vegetable</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>Some computers are laptops. All laptops are devices. Conclusion?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some computers are devices</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All computers are devices</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All devices are laptops</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3221,22 +3221,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some computers are devices</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>No V is W, so some T are not W.</t>
+          <t>Some computers → laptops → devices</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
+          <t>Some doctors are rich. All rich people are happy. Are some doctors happy?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3266,72 +3266,72 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>No L is M, so some J not M.</t>
+          <t>Some doctors are rich and rich people are happy.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Some P are Q. No Q is R. Are some P not R?</t>
+          <t>All cats are animals. All animals are living beings. Conclusions: I. Some cats are living beings. II. All living beings are cats.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>No Q is R, so some P not R.</t>
+          <t>Cats ⊂ animals ⊂ living beings.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>No S is T. Some T are U. All U are V. Are some S not V?</t>
+          <t>All stars are hot. Some hot things are bright. Conclusion?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All stars are bright</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some stars are bright</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some stars are hot</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some stars are hot</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>No S is T, so some S not V.</t>
+          <t>All stars → hot</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>Some P are Q. No Q is R. Are some P not R?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Because some Z not X, some Y not X.</t>
+          <t>No Q is R, so some P not R.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
+          <t>Some M are N. No N is O. All O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3432,11 +3432,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>No M is N. Some N are O. All O are P. Are some M not P?</t>
+          <t>Some fruits are sweet. All sweets are tasty. Are some fruits tasty?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>No conclusive data.</t>
+          <t>Some fruits are sweet and sweets are tasty.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
+          <t>Some students are hardworking. All hardworking people achieve success. Do some students achieve success?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3506,97 +3506,97 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Because no Z is W and some Y are Z, some X may not be W.</t>
+          <t>Some students are hardworking who achieve success.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>No A is B. All B are C. Some C are D. Are some A not D?</t>
+          <t>All poets are writers. Some writers are artists. Conclusions: I. Some poets are artists. II. All poets are artists.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>No direct link between A and D.</t>
+          <t>Writers ≠ artists by default.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Some M are N. No N is O. All O are P. Are some M not P?</t>
+          <t>No train is plane. All planes are fast. Conclusions: I. No train is fast. II. Some fast are planes.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Statement I overextends logic.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>All J are K. Some K are L. No L is M. Are some J not M?</t>
+          <t>Some teachers are strict. All strict people are effective. Are some teachers effective?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3626,17 +3626,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Since no L is M, some J not M.</t>
+          <t>Some teachers are strict and strict people are effective.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>Some trees are tall. All tall things cast shadows. Are some trees casting shadows?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some trees are tall and tall things cast shadows.</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
+          <t>No flowers are trees. Some trees are plants. Are some flowers plants?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>No R is S, so some P not S.</t>
+          <t>No direct relation given between flowers and plants.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Because no H is I, some F not I.</t>
+          <t>Some Z not X implies some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
+          <t>Some men are doctors. All doctors help people. Do some men help people?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3821,102 +3821,102 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>No direct info.</t>
+          <t>Some men are doctors who help people.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>All kings are rulers. No ruler is weak. Conclusions: I. No king is weak. II. All weak are kings.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>No V is W, so some T not W.</t>
+          <t>Exclusive trait of group extends to all members.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>Some fruits are mangoes. All mangoes are yellow. Conclusions: I. Some fruits are yellow. II. All fruits are mangoes.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Because some Z not X, some Y not X.</t>
+          <t>Through mangoes, yellow connection inferred.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
+          <t>No cats are dogs. All dogs are animals. Are no cats animals?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>No conclusive data.</t>
+          <t>No info on cats and animals.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>Some men are honest. All honest people are respected. Are some men respected?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3981,22 +3981,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some men are honest and honest people are respected.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
+          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4026,32 +4026,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>No direct info.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>All roses are flowers. No flower is tree. Conclusion?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some roses are trees</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No rose is tree</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All trees are flowers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No rose is tree</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>All roses → flowers, and no flower → tree</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
+          <t>Some cars are fast. All fast things are expensive. Are some cars expensive?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>No R is S, so some P not S.</t>
+          <t>Some cars are fast and fast things are expensive.</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>Some students are intelligent. All intelligent people succeed. Do some students succeed?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4141,22 +4141,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Some students are intelligent who succeed.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>No H is I, so some F not I.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
+          <t>No chairs are tables. All tables are furniture. Are no chairs furniture?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4226,57 +4226,57 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No conclusive info.</t>
+          <t>No info about chairs and furniture.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>All flowers are plants. Some plants are green. Conclusions: I. All flowers are green. II. Some flowers are green.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>No V is W, so some T not W.</t>
+          <t>Cannot determine specific intersection from partial.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All birds have feathers. Some birds are colorful. Are some colorful things having feathers?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4301,22 +4301,22 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Some Z not X implies some Y not X.</t>
+          <t>No direct info on colorful things and feathers.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
+          <t>No bats are birds. All birds can fly. Are no bats able to fly?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>No direct conclusion.</t>
+          <t>No info on bats' flying ability here.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>Some cats are black. All black are wild. Conclusion?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some cats are wild</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All cats are wild</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some black are cats</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some cats are wild</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Some cats → black → wild</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
+          <t>No F is G. All G are H. Some H are I. Are some F not I?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>No info.</t>
+          <t>No direct info on F and I.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>No fish are birds. All birds have wings. Are no fish have wings?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4466,72 +4466,72 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>No info on fish and wings.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>All dogs are animals. All animals are living beings. What can we conclude?</t>
+          <t>All engineers are professionals. Some professionals are teachers. Conclusions: I. Some engineers are teachers. II. All engineers are teachers.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>All dogs are living beings</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>All living beings are dogs</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Some animals are not dogs</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>All dogs are living beings</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>A → B → C means A → C</t>
+          <t>Overlap can’t be assumed.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Some birds are parrots. All parrots are green. What can we say?</t>
+          <t>All A are B. Some C are not B. Can some C be A?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Some birds are green</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>All green are parrots</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Some parrots are birds</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4541,77 +4541,77 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Some parrots are birds</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Some birds → parrots</t>
+          <t>Since some C are not B, some C might or might not be A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are sweet. What follows?</t>
+          <t>All birds can fly. Some birds are colorful. Are some colorful things flying?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Some apples are sweet</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>All sweet are fruits</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Some fruits are apples</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>All apples are sweet</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Some fruits are apples</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>All apples → fruits, so some fruits ← apples</t>
+          <t>No direct info on colorful things and flying.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Some boys are students. All students are intelligent. What follows?</t>
+          <t>Some birds are parrots. All parrots are green. What can we say?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>All boys are intelligent</t>
+          <t>Some birds are green</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Some boys are intelligent</t>
+          <t>All green are parrots</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>All intelligent are students</t>
+          <t>Some parrots are birds</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4621,77 +4621,77 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Some boys are intelligent</t>
+          <t>Some parrots are birds</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Some boys → students → intelligent</t>
+          <t>Some birds → parrots</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>No pen is pencil. All pencils are blue. Conclusion?</t>
+          <t>Some buses are cars. All cars are vehicles. Conclusions: I. Some buses are vehicles. II. All vehicles are buses.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Some pens are blue</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>No pen is blue</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>All blue are pencils</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>No connection between pen and blue</t>
+          <t>Transitive link holds.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Some cats are black. All black are wild. Conclusion?</t>
+          <t>No students are lazy. Some lazy people are careless. Are no students careless?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Some cats are wild</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>All cats are wild</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Some black are cats</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Some cats are wild</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Some cats → black → wild</t>
+          <t>No info on students and careless.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>All roses are flowers. No flower is tree. Conclusion?</t>
+          <t>Some chairs are tables. All tables are wood. Conclusions: I. Some chairs are wood. II. All wood are tables.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Some roses are trees</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>No rose is tree</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>All trees are flowers</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>No rose is tree</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>All roses → flowers, and no flower → tree</t>
+          <t>'Some' does not imply full connection unless supported.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>No lion is a deer. Some deer are animals. Conclusion?</t>
+          <t>All roses are flowers. Some flowers are fragrant. Are all roses fragrant?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>No lion is an animal</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Some lions are deer</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>No deer is lion</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4781,37 +4781,37 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>No deer is lion</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>No lion → deer = No deer → lion</t>
+          <t>Only some flowers are fragrant, no info if roses are.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Some books are novels. All novels are fiction. Conclusion?</t>
+          <t>No cars are bicycles. Some bicycles are two-wheelers. Are no cars two-wheelers?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Some books are fiction</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>All books are fiction</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>All fiction are novels</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4821,77 +4821,77 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Some books are fiction</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Some books → novels → fiction</t>
+          <t>No info on cars and two-wheelers.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>All fruits are healthy. Some healthy are tasty. Conclusion?</t>
+          <t>All pens are books. Some books are papers. Conclusions: I. Some pens are papers. II. All books are pens.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Some fruits are tasty</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>All healthy are fruits</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Some fruits are healthy</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>All tasty are fruits</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Some fruits are healthy</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>All fruits → healthy</t>
+          <t>You cannot conclude direct relation unless explicitly stated.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Some chairs are wooden. All wooden are brown. Conclusion?</t>
+          <t>All rivers are water bodies. Some water bodies are dirty. Are some rivers dirty?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>All chairs are brown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Some chairs are brown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Some wooden are chairs</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4901,37 +4901,37 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Some chairs are brown</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Some chairs → wooden → brown</t>
+          <t>No direct info on rivers and dirty.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>No fish is bird. All birds can fly. Conclusion?</t>
+          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No fish can fly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>All fish are birds</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Some fish can fly</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4941,77 +4941,77 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>No fish can fly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>No fish → bird → fly</t>
+          <t>Because no Z is W, and some Y are Z, some X may not be W.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>All pens are objects. Some objects are useful. Conclusion?</t>
+          <t>Some pencils are red. No red is blue. Conclusions: I. No pencil is blue. II. Some pencils are not blue.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Some pens are useful</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>All useful are pens</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Some objects are pens</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Some objects are pens</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>All pens → objects</t>
+          <t>Some pencils overlap red, which ≠ blue.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Some teachers are writers. All writers are creative. Conclusion?</t>
+          <t>Some birds are flying creatures. All flying creatures can fly. Can some birds fly?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Some teachers are creative</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>All teachers are creative</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Some creative are teachers</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5021,157 +5021,157 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Some teachers are creative</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Some teachers → writers → creative</t>
+          <t>Some birds belong to flying creatures which can fly.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>No apple is orange. All oranges are juicy. Conclusion?</t>
+          <t>Some mobiles are gadgets. All gadgets are expensive. Conclusions: I. Some mobiles are expensive. II. All mobiles are gadgets.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No apple is juicy</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Some apples are juicy</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>All apples are oranges</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>No link between apple and juicy</t>
+          <t>Indirect connection possible for subset.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>All bats are mammals. Some mammals are nocturnal. Conclusion?</t>
+          <t>Some birds are parrots. Some parrots are green. Conclusions: I. Some birds are green. II. Some green are parrots.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Some bats are nocturnal</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>All bats are nocturnal</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Some mammals are bats</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Some mammals are bats</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>All bats → mammals</t>
+          <t>Direct overlap of some parrots and green.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Some girls are dancers. All dancers are flexible. Conclusion?</t>
+          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>All girls are flexible</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Some dancers are girls</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Some girls are flexible</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>All flexible are girls</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Some girls are flexible</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Some girls → dancers → flexible</t>
+          <t>No direct conclusion.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>All mangoes are fruits. No fruit is vegetable. Conclusion?</t>
+          <t>Some P are Q. No Q is R. Are some P not R?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Some mangoes are vegetables</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>All mangoes are vegetables</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>No mango is vegetable</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5181,37 +5181,37 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>No mango is vegetable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>All mangoes → fruits, and no fruit → vegetable</t>
+          <t>Since no Q is R, some P may not be R.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>No table is chair. All chairs are wooden. Conclusion?</t>
+          <t>No pencils are erasers. All erasers are stationery. Are no pencils stationery?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Some tables are wooden</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>No table is wooden</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>No chair is table</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5221,77 +5221,77 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>No chair is table</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>No table → chair = No chair → table</t>
+          <t>No info on pencils and stationery relation.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Some computers are laptops. All laptops are devices. Conclusion?</t>
+          <t>Some dogs are cats. No cat is rabbit. Conclusions: I. Some dogs are rabbits. II. No dog is rabbit.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Some computers are devices</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>All computers are devices</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>All devices are laptops</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Some computers are devices</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Some computers → laptops → devices</t>
+          <t>Insufficient link between groups.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>All birds are animals. Some animals are flying. Conclusion?</t>
+          <t>No cats are mice. All mice are small. Are no cats small?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Some birds are flying</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>All animals are birds</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>All birds are flying</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5301,37 +5301,37 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Some birds are flying</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>All birds → animals → some flying</t>
+          <t>No info on cats and small.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Some toys are plastic. All plastic is harmful. Conclusion?</t>
+          <t>No doctors are lawyers. Some lawyers are teachers. Are some doctors teachers?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Some toys are harmful</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>All toys are harmful</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Some harmful are toys</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5341,117 +5341,117 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Some toys are harmful</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Some toys → plastic → harmful</t>
+          <t>No direct relation between doctors and teachers.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>All stars are hot. Some hot things are bright. Conclusion?</t>
+          <t>Some boys are girls. Some girls are intelligent. Conclusions: I. Some boys are intelligent. II. All boys are intelligent.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>All stars are bright</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Some stars are bright</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Some stars are hot</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Some stars are hot</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>All stars → hot</t>
+          <t>No definite relation proven across categories.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>No tree is stone. Some stones are heavy. Conclusion?</t>
+          <t>Some cups are plates. All plates are spoons. Conclusions: I. Some cups are spoons. II. All spoons are cups.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>No tree is heavy</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Some trees are heavy</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>All stones are trees</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>No connection between tree and heavy</t>
+          <t>Some indirect overlap is inferred.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Some pencils are long. All long things are thin. Conclusion?</t>
+          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Some pencils are thin</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>All pencils are thin</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Some thin things are pencils</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5461,22 +5461,22 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Some pencils are thin</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Some pencils → long → thin</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>All dogs are animals. Some animals are cats. Conclusions: I. Some dogs are cats. II. All animals are dogs.</t>
+          <t>All goats are mammals. All mammals are animals. Conclusions: I. All goats are animals. II. All animals are goats.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5501,262 +5501,262 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Only the conclusions logically follow based on statements.</t>
+          <t>Proper direction of deduction matters.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Some pens are pencils. All pencils are erasers. Conclusions: I. Some pens are erasers. II. All erasers are pencils.</t>
+          <t>No tree is stone. Some stones are heavy. Conclusion?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No tree is heavy</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some trees are heavy</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All stones are trees</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Some pens overlap with erasers due to common pencils.</t>
+          <t>No connection between tree and heavy</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>All cars are vehicles. All trucks are vehicles. Conclusions: I. Some trucks are cars. II. All cars are trucks.</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Common class doesn’t mean crossover between groups.</t>
+          <t>Because some Z are not X, and some Y are Z, some Y may not be X.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>All boys are students. Some students are girls. Conclusions: I. Some boys are girls. II. All girls are students.</t>
+          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Some students are girls, so some girls are students.</t>
+          <t>No H is I, so some F not I.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Some apples are fruits. All fruits are juicy. Conclusions: I. Some apples are juicy. II. All juicy things are fruits.</t>
+          <t>All students are learners. Some learners are athletes. Are some students athletes?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Partial overlap with juicy items.</t>
+          <t>No direct info on students and athletes.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Some tables are chairs. No chair is sofa. Conclusions: I. Some tables are not sofas. II. No table is sofa.</t>
+          <t>Some boys are students. All students study. Do some boys study?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>We know chairs ≠ sofa; table partially overlaps.</t>
+          <t>Some boys belong to students who study.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>No bird is mammal. All mammals are warm-blooded. Conclusions: I. No bird is warm-blooded. II. Some warm-blooded are mammals.</t>
+          <t>Some flowers are red. All red things are attractive. Are some flowers attractive?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>All mammals ⊂ warm-blooded, so II true.</t>
+          <t>Some flowers are red and red things are attractive.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Some cups are plates. All plates are spoons. Conclusions: I. Some cups are spoons. II. All spoons are cups.</t>
+          <t>All cats are animals. All animals are mammals. Conclusions: I. All cats are mammals. II. All mammals are cats.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None follow</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5786,47 +5786,47 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Some indirect overlap is inferred.</t>
+          <t>All members of first category are also members of the final category.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>All roses are flowers. Some flowers are red. Conclusions: I. Some roses are red. II. All red things are flowers.</t>
+          <t>No apple is orange. All oranges are juicy. Conclusion?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No apple is juicy</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some apples are juicy</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All apples are oranges</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Overlap cannot be confirmed.</t>
+          <t>No link between apple and juicy</t>
         </is>
       </c>
     </row>
@@ -5836,87 +5836,87 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>All windows are doors. Some doors are walls. Conclusions: I. Some windows are walls. II. Some doors are windows.</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Some doors are windows due to inclusion.</t>
+          <t>No V is W, so some T not W.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Some keys are locks. Some locks are doors. Conclusions: I. Some keys are doors. II. All keys are doors.</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>No definite connection between keys and doors.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are living beings. Conclusions: I. Some cats are living beings. II. All living beings are cats.</t>
+          <t>All actors are performers. No performer is lazy. Conclusions: I. No actor is lazy. II. Some lazy are actors.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Cats ⊂ animals ⊂ living beings.</t>
+          <t>Subset retains universal trait.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>No pen is marker. All markers are tools. Conclusions: I. Some pens are not tools. II. No marker is pen.</t>
+          <t>Some boys are singers. All singers are dancers. Conclusions: I. Some boys are dancers. II. All dancers are boys.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5981,22 +5981,22 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Negative statement from given facts.</t>
+          <t>Some boys overlap dancers via singers.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Some birds are parrots. Some parrots are green. Conclusions: I. Some birds are green. II. Some green are parrots.</t>
+          <t>All dogs are animals. Some animals are cats. Conclusions: I. Some dogs are cats. II. All animals are dogs.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6021,92 +6021,92 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Direct overlap of some parrots and green.</t>
+          <t>Only the conclusions logically follow based on statements.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>All stones are rocks. Some rocks are heavy. Conclusions: I. Some stones are heavy. II. All heavy are rocks.</t>
+          <t>All pens are objects. Some objects are useful. Conclusion?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some pens are useful</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All useful are pens</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some objects are pens</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some objects are pens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Overlap is not definite.</t>
+          <t>All pens → objects</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Some pencils are red. No red is blue. Conclusions: I. No pencil is blue. II. Some pencils are not blue.</t>
+          <t>Some chairs are wooden. All wooden are brown. Conclusion?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All chairs are brown</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some chairs are brown</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some wooden are chairs</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some chairs are brown</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Some pencils overlap red, which ≠ blue.</t>
+          <t>Some chairs → wooden → brown</t>
         </is>
       </c>
     </row>
@@ -6116,127 +6116,127 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>All cows are animals. All animals are herbivores. Conclusions: I. Some cows are herbivores. II. All cows are herbivores.</t>
+          <t>Some girls are dancers. All dancers are flexible. Conclusion?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All girls are flexible</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some dancers are girls</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some girls are flexible</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>All flexible are girls</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some girls are flexible</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Cows ⊂ animals ⊂ herbivores.</t>
+          <t>Some girls → dancers → flexible</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>No chair is desk. Some desks are tables. Conclusions: I. No chair is table. II. Some tables are not chairs.</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Partial exclusion inferred.</t>
+          <t>No conclusive relation.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>All engineers are professionals. Some professionals are teachers. Conclusions: I. Some engineers are teachers. II. All engineers are teachers.</t>
+          <t>No M is N. Some N are O. All O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Overlap can’t be assumed.</t>
+          <t>No conclusive data.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Some fruits are mangoes. All mangoes are yellow. Conclusions: I. Some fruits are yellow. II. All fruits are mangoes.</t>
+          <t>No apple is banana. Some bananas are yellow. Conclusions: I. Some apples are yellow. II. No apple is yellow.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Through mangoes, yellow connection inferred.</t>
+          <t>No definite apple-yellow link.</t>
         </is>
       </c>
     </row>
@@ -6276,127 +6276,127 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>All lions are animals. No animal is plant. Conclusions: I. No lion is plant. II. All lions are plants.</t>
+          <t>All birds are animals. Some animals are flying. Conclusion?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some birds are flying</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All animals are birds</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All birds are flying</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some birds are flying</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lions ⊂ animals, animals ≠ plants.</t>
+          <t>All birds → animals → some flying</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Some boys are singers. All singers are dancers. Conclusions: I. Some boys are dancers. II. All dancers are boys.</t>
+          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Some boys overlap dancers via singers.</t>
+          <t>Since no L is M and some L are K, some J may not be M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>No apple is banana. Some bananas are yellow. Conclusions: I. Some apples are yellow. II. No apple is yellow.</t>
+          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>No definite apple-yellow link.</t>
+          <t>No info.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>All poets are writers. Some writers are artists. Conclusions: I. Some poets are artists. II. All poets are artists.</t>
+          <t>Some pens are pencils. All pencils are erasers. Conclusions: I. Some pens are erasers. II. All erasers are pencils.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6421,252 +6421,252 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Writers ≠ artists by default.</t>
+          <t>Some pens overlap with erasers due to common pencils.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Some teachers are doctors. All doctors are professionals. Conclusions: I. Some teachers are professionals. II. All professionals are doctors.</t>
+          <t>No X is Y. All Y are Z. Are some Z not X?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Partial link via doctors.</t>
+          <t>Since no X is Y and all Y are Z, some Z are not X.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are mammals. Conclusions: I. All cats are mammals. II. All mammals are cats.</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>None follow</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>All members of first category are also members of the final category.</t>
+          <t>No V is W, so some T not W.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>All pens are books. Some books are papers. Conclusions: I. Some pens are papers. II. All books are pens.</t>
+          <t>All flowers are plants. Some plants are medicinal. Are all flowers medicinal?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>You cannot conclude direct relation unless explicitly stated.</t>
+          <t>Only some plants are medicinal.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Some apples are fruits. All fruits are healthy. Conclusions: I. Some apples are healthy. II. All apples are healthy.</t>
+          <t>All apples are fruits. Some fruits are red. Are some apples red?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Part of a group being linked to another through common element.</t>
+          <t>No direct info on apples and red.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>All dogs are loyal. No loyal being is dishonest. Conclusions: I. No dog is dishonest. II. All dishonest are dogs.</t>
+          <t>All dogs are animals. All animals are living beings. What can we conclude?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All dogs are living beings</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All living beings are dogs</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some animals are not dogs</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All dogs are living beings</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>No and "All" combined can show exclusivity.</t>
+          <t>A → B → C means A → C</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Some chairs are tables. All tables are wood. Conclusions: I. Some chairs are wood. II. All wood are tables.</t>
+          <t>All M are N. Some N are O. No O is P. Are some M not P?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>'Some' does not imply full connection unless supported.</t>
+          <t>Some M could belong to N which belong to O; none O is P, so some M are not P.</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>All flowers are plants. Some plants are green. Conclusions: I. All flowers are green. II. Some flowers are green.</t>
+          <t>Some tables are chairs. No chair is sofa. Conclusions: I. Some tables are not sofas. II. No table is sofa.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6701,62 +6701,62 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Cannot determine specific intersection from partial.</t>
+          <t>We know chairs ≠ sofa; table partially overlaps.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>No bird is insect. All parrots are birds. Conclusions: I. No parrot is insect. II. Some insects are birds.</t>
+          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Parrot subset inherits bird restriction.</t>
+          <t>Because no Z is W and some Y are Z, some X may not be W.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>All lions are wild. No wild is pet. Conclusions: I. No lion is pet. II. Some lions are pets.</t>
+          <t>All roses are red. Some red things are beautiful. Conclusions: I. Some roses are beautiful. II. All red things are roses.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6781,182 +6781,182 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Categorical exclusion carries to subset.</t>
+          <t>Common trait not confirmed for subset.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Some boys are girls. Some girls are intelligent. Conclusions: I. Some boys are intelligent. II. All boys are intelligent.</t>
+          <t>Some boys are tall. All tall people are strong. Are some boys strong?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>No definite relation proven across categories.</t>
+          <t>Some boys are tall and tall people are strong.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>All pens are pencils. No pencil is marker. Conclusions: I. No pen is marker. II. Some markers are pens.</t>
+          <t>Some books are novels. All novels are fiction. Conclusion?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some books are fiction</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All books are fiction</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All fiction are novels</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some books are fiction</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Transitive exclusion applies.</t>
+          <t>Some books → novels → fiction</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>All goats are mammals. All mammals are animals. Conclusions: I. All goats are animals. II. All animals are goats.</t>
+          <t>No dogs are cats. All cats are animals. Are no dogs animals?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Proper direction of deduction matters.</t>
+          <t>We cannot conclude about dogs being animals.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Some mangoes are sweet. All sweet things are healthy. Conclusions: I. Some mangoes are healthy. II. All mangoes are healthy.</t>
+          <t>All J are K. Some K are L. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Indirect conclusion from overlap.</t>
+          <t>Since no L is M, some J not M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>All actors are performers. No performer is lazy. Conclusions: I. No actor is lazy. II. Some lazy are actors.</t>
+          <t>All pens are pencils. No pencil is marker. Conclusions: I. No pen is marker. II. Some markers are pens.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6986,87 +6986,87 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Subset retains universal trait.</t>
+          <t>Transitive exclusion applies.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>All roses are red. Some red things are beautiful. Conclusions: I. Some roses are beautiful. II. All red things are roses.</t>
+          <t>Some K are L. Some L are M. No M is N. Are some K not N?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Common trait not confirmed for subset.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Some buses are cars. All cars are vehicles. Conclusions: I. Some buses are vehicles. II. All vehicles are buses.</t>
+          <t>No pen is pencil. All pencils are blue. Conclusion?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some pens are blue</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No pen is blue</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All blue are pencils</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Transitive link holds.</t>
+          <t>No connection between pen and blue</t>
         </is>
       </c>
     </row>
@@ -7076,287 +7076,287 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>All kids are students. No student is teacher. Conclusions: I. No kid is teacher. II. Some teachers are students.</t>
+          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Exclusion travels to subgroup.</t>
+          <t>No R is S, so some P not S.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>No train is plane. All planes are fast. Conclusions: I. No train is fast. II. Some fast are planes.</t>
+          <t>No dogs are cats. All cats are pets. Are no dogs pets?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Statement I overextends logic.</t>
+          <t>No info on dogs and pets.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>All men are humans. Some humans are kind. Conclusions: I. Some men are kind. II. All men are kind.</t>
+          <t>Some teachers are writers. All writers are creative. Conclusion?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some teachers are creative</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All teachers are creative</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some creative are teachers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some teachers are creative</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Some does not apply across unless proven.</t>
+          <t>Some teachers → writers → creative</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Some books are pens. Some pens are colors. Conclusions: I. Some books are colors. II. All colors are pens.</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Indirect link not confirmed.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>All kings are rulers. No ruler is weak. Conclusions: I. No king is weak. II. All weak are kings.</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Exclusive trait of group extends to all members.</t>
+          <t>No conclusive relation between M and P.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>All squares are rectangles. All rectangles are shapes. Conclusions: I. All squares are shapes. II. Some shapes are squares.</t>
+          <t>All cats are animals. All animals are living beings. Are all cats living beings?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Multiple logical links proven.</t>
+          <t>If all cats are animals and all animals are living beings, all cats are living beings.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Some mobiles are gadgets. All gadgets are expensive. Conclusions: I. Some mobiles are expensive. II. All mobiles are gadgets.</t>
+          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Indirect connection possible for subset.</t>
+          <t>Because no H is I, some F not I.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>All apples are fruits. No fruit is vegetable. Conclusions: I. No apple is vegetable. II. Some apples are vegetables.</t>
+          <t>All boys are students. Some students are girls. Conclusions: I. Some boys are girls. II. All girls are students.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7381,92 +7381,92 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Exclusive property holds.</t>
+          <t>Some students are girls, so some girls are students.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Some dogs are cats. No cat is rabbit. Conclusions: I. Some dogs are rabbits. II. No dog is rabbit.</t>
+          <t>No books are newspapers. Some newspapers are daily. Are no books daily?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Insufficient link between groups.</t>
+          <t>No info on books being daily.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>All paper is white. Some white is light. Conclusions: I. Some paper is light. II. All light is white.</t>
+          <t>Some fruits are apples. All apples are red. Are some fruits red?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>No guaranteed overlap shown.</t>
+          <t>If some fruits are apples and apples are red, some fruits are red.</t>
         </is>
       </c>
     </row>

--- a/Data/Sylogism.xlsx
+++ b/Data/Sylogism.xlsx
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
+          <t>Some flowers are red. All red things are attractive. Are some flowers attractive?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,102 +501,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Some flowers are red and red things are attractive.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>All stones are rocks. Some rocks are heavy. Conclusions: I. Some stones are heavy. II. All heavy are rocks.</t>
+          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Overlap is not definite.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>All flowers are beautiful. Some beautiful things are expensive. Are some flowers expensive?</t>
+          <t>Some boys are girls. Some girls are intelligent. Conclusions: I. Some boys are intelligent. II. All boys are intelligent.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No direct info about flowers and expensive.</t>
+          <t>No definite relation proven across categories.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Some engineers are scientists. No scientist is artist. Are some engineers not artists?</t>
+          <t>No D is E. Some F are D. All F are G. Are some G not E?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -626,137 +626,137 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Engineers partly overlap scientists; scientists exclude artists.</t>
+          <t>Since no D is E and some F are D, some G (which include F) are not E.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>All actors are dancers. Some dancers are singers. Can we conclude some actors are singers?</t>
+          <t>All poets are writers. Some writers are artists. Conclusions: I. Some poets are artists. II. All poets are artists.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Partial overlap between dancers and singers; actors may or may not be singers.</t>
+          <t>Writers ≠ artists by default.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>No pen is marker. All markers are tools. Conclusions: I. Some pens are not tools. II. No marker is pen.</t>
+          <t>All pens are useful. Some useful things are costly. Are some pens costly?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Negative statement from given facts.</t>
+          <t>No direct info on pens and costly.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>All men are humans. Some humans are kind. Conclusions: I. Some men are kind. II. All men are kind.</t>
+          <t>No tree is stone. Some stones are heavy. Conclusion?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No tree is heavy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some trees are heavy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All stones are trees</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Some does not apply across unless proven.</t>
+          <t>No connection between tree and heavy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>No bird is mammal. All mammals are warm-blooded. Conclusions: I. No bird is warm-blooded. II. Some warm-blooded are mammals.</t>
+          <t>Some buses are cars. All cars are vehicles. Conclusions: I. Some buses are vehicles. II. All vehicles are buses.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -781,62 +781,62 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>All mammals ⊂ warm-blooded, so II true.</t>
+          <t>Transitive link holds.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Some teachers are doctors. All doctors are professionals. Conclusions: I. Some teachers are professionals. II. All professionals are doctors.</t>
+          <t>All roses are flowers. Some flowers are fragrant. Are all roses fragrant?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Partial link via doctors.</t>
+          <t>Only some flowers are fragrant, no info if roses are.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -866,137 +866,137 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No R is S, so some P not S.</t>
+          <t>Because some Z not X, some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Some apples are fruits. All fruits are juicy. Conclusions: I. Some apples are juicy. II. All juicy things are fruits.</t>
+          <t>Some trees are tall. All tall things cast shadows. Are some trees casting shadows?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Partial overlap with juicy items.</t>
+          <t>Some trees are tall and tall things cast shadows.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Some books are pens. Some pens are colors. Conclusions: I. Some books are colors. II. All colors are pens.</t>
+          <t>All apples are fruits. Some fruits are sweet. What follows?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some apples are sweet</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All sweet are fruits</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some fruits are apples</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>All apples are sweet</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some fruits are apples</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Indirect link not confirmed.</t>
+          <t>All apples → fruits, so some fruits ← apples</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No cars are bikes. All bikes are fast. Are no cars fast?</t>
+          <t>All engineers are professionals. Some professionals are teachers. Conclusions: I. Some engineers are teachers. II. All engineers are teachers.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No info on cars and fast relation.</t>
+          <t>Overlap can’t be assumed.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Because some Z not X, some Y not X.</t>
+          <t>No L is M, so some J not M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>No S is T. Some T are U. All U are V. Are some S not V?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1066,57 +1066,57 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No S is T, so some S not V.</t>
+          <t>Some Z not X implies some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>All lions are wild. No wild is pet. Conclusions: I. No lion is pet. II. Some lions are pets.</t>
+          <t>No students are lazy. Some lazy people are careless. Are no students careless?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Categorical exclusion carries to subset.</t>
+          <t>No info on students and careless.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>All lions are animals. Some animals are wild. Are all lions wild?</t>
+          <t>No chairs are tables. All tables are furniture. Are no chairs furniture?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1146,32 +1146,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Only some animals are wild.</t>
+          <t>No info about chairs and furniture.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>No lion is a deer. Some deer are animals. Conclusion?</t>
+          <t>All birds have feathers. Some birds are colorful. Are some colorful things having feathers?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No lion is an animal</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Some lions are deer</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No deer is lion</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No deer is lion</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No lion → deer = No deer → lion</t>
+          <t>No direct info on colorful things and feathers.</t>
         </is>
       </c>
     </row>
@@ -1196,127 +1196,127 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>All men are humans. Some humans are kind. Conclusions: I. Some men are kind. II. All men are kind.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No conclusion.</t>
+          <t>Some does not apply across unless proven.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>No bird is insect. All parrots are birds. Conclusions: I. No parrot is insect. II. Some insects are birds.</t>
+          <t>All A are B. Some C are not B. Can some C be A?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Parrot subset inherits bird restriction.</t>
+          <t>Since some C are not B, some C might or might not be A.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>All cars are vehicles. Some vehicles are fast. Are all cars fast?</t>
+          <t>Some girls are dancers. All dancers are flexible. Conclusion?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All girls are flexible</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some dancers are girls</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some girls are flexible</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>All flexible are girls</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some girls are flexible</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Only some vehicles are fast, no info about cars.</t>
+          <t>Some girls → dancers → flexible</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Some books are novels. All novels are stories. Are some books stories?</t>
+          <t>Some men are honest. All honest people are respected. Are some men respected?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1346,97 +1346,97 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Some books belong to novels which are stories.</t>
+          <t>Some men are honest and honest people are respected.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Some boys are students. All students are intelligent. What follows?</t>
+          <t>All cats are animals. All animals are mammals. Conclusions: I. All cats are mammals. II. All mammals are cats.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>All boys are intelligent</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Some boys are intelligent</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>All intelligent are students</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>None follow</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Some boys are intelligent</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Some boys → students → intelligent</t>
+          <t>All members of first category are also members of the final category.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>All dogs are loyal. No loyal being is dishonest. Conclusions: I. No dog is dishonest. II. All dishonest are dogs.</t>
+          <t>All bats are mammals. Some mammals are nocturnal. Conclusion?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some bats are nocturnal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All bats are nocturnal</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some mammals are bats</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some mammals are bats</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No and "All" combined can show exclusivity.</t>
+          <t>All bats → mammals</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>No A is B. All B are C. Some C are D. Are some A not D?</t>
+          <t>All apples are fruits. Some fruits are sour. Are some apples sour?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No direct link between A and D.</t>
+          <t>No info on apples being sour.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
+          <t>Some teachers are writers. All writers are creative. Conclusion?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some teachers are creative</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All teachers are creative</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some creative are teachers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1501,22 +1501,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some teachers are creative</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some teachers → writers → creative</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Some apples are fruits. All fruits are healthy. Conclusions: I. Some apples are healthy. II. All apples are healthy.</t>
+          <t>Some tables are chairs. No chair is sofa. Conclusions: I. Some tables are not sofas. II. No table is sofa.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1546,87 +1546,87 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Part of a group being linked to another through common element.</t>
+          <t>We know chairs ≠ sofa; table partially overlaps.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
+          <t>All lions are animals. No animal is plant. Conclusions: I. No lion is plant. II. All lions are plants.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No L is M, so some J not M.</t>
+          <t>Lions ⊂ animals, animals ≠ plants.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are sweet. What follows?</t>
+          <t>Some men are doctors. All doctors help people. Do some men help people?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Some apples are sweet</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>All sweet are fruits</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Some fruits are apples</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>All apples are sweet</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Some fruits are apples</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All apples → fruits, so some fruits ← apples</t>
+          <t>Some men are doctors who help people.</t>
         </is>
       </c>
     </row>
@@ -1672,66 +1672,66 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>All squares are rectangles. All rectangles are shapes. Conclusions: I. All squares are shapes. II. Some shapes are squares.</t>
+          <t>All flowers are plants. Some plants are medicinal. Are all flowers medicinal?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Multiple logical links proven.</t>
+          <t>Only some plants are medicinal.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>No fish is bird. All birds can fly. Conclusion?</t>
+          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No fish can fly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>All fish are birds</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Some fish can fly</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1741,22 +1741,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No fish can fly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>No fish → bird → fly</t>
+          <t>Because no H is I, some F not I.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>All cars are vehicles. Some vehicles are expensive. Are all cars expensive?</t>
+          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1786,32 +1786,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Some vehicles are expensive, cars may or may not be expensive.</t>
+          <t>No conclusive data.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>No table is chair. All chairs are wooden. Conclusion?</t>
+          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Some tables are wooden</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>No table is wooden</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>No chair is table</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1821,22 +1821,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No chair is table</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>No table → chair = No chair → table</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
+          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1866,32 +1866,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No conclusive info.</t>
+          <t>No direct conclusion.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Some toys are plastic. All plastic is harmful. Conclusion?</t>
+          <t>Some students are intelligent. All intelligent people succeed. Do some students succeed?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Some toys are harmful</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>All toys are harmful</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Some harmful are toys</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Some toys are harmful</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Some toys → plastic → harmful</t>
+          <t>Some students are intelligent who succeed.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are sour. Are some apples sour?</t>
+          <t>Some teachers are doctors. All doctors are professionals. Conclusions: I. Some teachers are professionals. II. All professionals are doctors.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>No info on apples being sour.</t>
+          <t>Partial link via doctors.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>Some fruits are apples. All apples are red. Are some fruits red?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1981,172 +1981,172 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>No direct conclusion can be drawn about A and D.</t>
+          <t>If some fruits are apples and apples are red, some fruits are red.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>All cars are vehicles. All trucks are vehicles. Conclusions: I. Some trucks are cars. II. All cars are trucks.</t>
+          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Common class doesn’t mean crossover between groups.</t>
+          <t>No conclusive info.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>Some birds are parrots. Some parrots are green. Conclusions: I. Some birds are green. II. Some green are parrots.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Direct overlap of some parrots and green.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>No books are papers. All papers are white. Are no books white?</t>
+          <t>All apples are fruits. No fruit is vegetable. Conclusions: I. No apple is vegetable. II. Some apples are vegetables.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>No info on books and white.</t>
+          <t>Exclusive property holds.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>All kids are students. No student is teacher. Conclusions: I. No kid is teacher. II. Some teachers are students.</t>
+          <t>All pens are objects. Some objects are useful. Conclusion?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some pens are useful</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All useful are pens</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some objects are pens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some objects are pens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Exclusion travels to subgroup.</t>
+          <t>All pens → objects</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>All apples are fruits. No fruit is vegetable. Conclusions: I. No apple is vegetable. II. Some apples are vegetables.</t>
+          <t>No apple is banana. Some bananas are yellow. Conclusions: I. Some apples are yellow. II. No apple is yellow.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2181,37 +2181,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Exclusive property holds.</t>
+          <t>No definite apple-yellow link.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>All bats are mammals. Some mammals are nocturnal. Conclusion?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Some bats are nocturnal</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>All bats are nocturnal</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Some mammals are bats</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2221,62 +2221,62 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Some mammals are bats</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>All bats → mammals</t>
+          <t>No conclusion.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Some mangoes are sweet. All sweet things are healthy. Conclusions: I. Some mangoes are healthy. II. All mangoes are healthy.</t>
+          <t>All J are K. Some K are L. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Indirect conclusion from overlap.</t>
+          <t>Since no L is M, some J not M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Some cars are red. All red things are bright. Are some cars bright?</t>
+          <t>All actors are dancers. Some dancers are singers. Can we conclude some actors are singers?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2301,22 +2301,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Some cars are red and red things are bright.</t>
+          <t>Partial overlap between dancers and singers; actors may or may not be singers.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>All windows are doors. Some doors are walls. Conclusions: I. Some windows are walls. II. Some doors are windows.</t>
+          <t>All paper is white. Some white is light. Conclusions: I. Some paper is light. II. All light is white.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2341,22 +2341,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Some doors are windows due to inclusion.</t>
+          <t>No guaranteed overlap shown.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>No S is R. Some R are Q. All Q are P. Are some P not S?</t>
+          <t>Some students are hardworking. All hardworking people achieve success. Do some students achieve success?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2386,57 +2386,57 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Since no S is R, some P which are Q and R are not S.</t>
+          <t>Some students are hardworking who achieve success.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>All lions are animals. No animal is plant. Conclusions: I. No lion is plant. II. All lions are plants.</t>
+          <t>All M are N. Some N are O. No O is P. Are some M not P?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Lions ⊂ animals, animals ≠ plants.</t>
+          <t>Some M could belong to N which belong to O; none O is P, so some M are not P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>No F is G. All G are H. Some H are I. Are some F not I?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2461,62 +2461,62 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Because some Z not X, some Y not X.</t>
+          <t>No direct info on F and I.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>No chair is desk. Some desks are tables. Conclusions: I. No chair is table. II. Some tables are not chairs.</t>
+          <t>All fruits are healthy. Some healthy are tasty. Conclusion?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some fruits are tasty</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All healthy are fruits</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some fruits are healthy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>All tasty are fruits</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some fruits are healthy</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Partial exclusion inferred.</t>
+          <t>All fruits → healthy</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>No D is E. Some F are D. All F are G. Are some G not E?</t>
+          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Since no D is E and some F are D, some G (which include F) are not E.</t>
+          <t>Because no Z is W and some Y are Z, some X may not be W.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>No S is R. Some R are Q. All Q are P. Are some P not S?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2586,57 +2586,57 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Since no V is W, some T which are U and U are V, are not W.</t>
+          <t>Since no S is R, some P which are Q and R are not S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>All fruits are healthy. Some healthy are tasty. Conclusion?</t>
+          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Some fruits are tasty</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>All healthy are fruits</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Some fruits are healthy</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>All tasty are fruits</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Some fruits are healthy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>All fruits → healthy</t>
+          <t>Because no Z is W, and some Y are Z, some X may not be W.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>All roses are flowers. Some flowers are red. Conclusions: I. Some roses are red. II. All red things are flowers.</t>
+          <t>All dogs are loyal. No loyal being is dishonest. Conclusions: I. No dog is dishonest. II. All dishonest are dogs.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2661,22 +2661,22 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Overlap cannot be confirmed.</t>
+          <t>No and "All" combined can show exclusivity.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>All cows are animals. All animals are herbivores. Conclusions: I. Some cows are herbivores. II. All cows are herbivores.</t>
+          <t>All actors are performers. No performer is lazy. Conclusions: I. No actor is lazy. II. Some lazy are actors.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2701,18 +2701,18 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Cows ⊂ animals ⊂ herbivores.</t>
+          <t>Subset retains universal trait.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2746,17 +2746,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No V is W, so some T are not W.</t>
+          <t>No V is W, so some T not W.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>Some P are Q. No Q is R. Are some P not R?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2781,22 +2781,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Since no Q is R, some P may not be R.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>All paper is white. Some white is light. Conclusions: I. Some paper is light. II. All light is white.</t>
+          <t>All windows are doors. Some doors are walls. Conclusions: I. Some windows are walls. II. Some doors are windows.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2821,62 +2821,62 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>No guaranteed overlap shown.</t>
+          <t>Some doors are windows due to inclusion.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Some keys are locks. Some locks are doors. Conclusions: I. Some keys are doors. II. All keys are doors.</t>
+          <t>Some engineers are scientists. No scientist is artist. Are some engineers not artists?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>No definite connection between keys and doors.</t>
+          <t>Engineers partly overlap scientists; scientists exclude artists.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>No conclusive data.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>No P is Q. All Q are R. Some R are S. Are some P not S?</t>
+          <t>Some boys are students. All students study. Do some boys study?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2941,62 +2941,62 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cannot conclude about P and S.</t>
+          <t>Some boys belong to students who study.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>All pens are useful. Some useful things are costly. Are some pens costly?</t>
+          <t>Some apples are fruits. All fruits are healthy. Conclusions: I. Some apples are healthy. II. All apples are healthy.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>No direct info on pens and costly.</t>
+          <t>Part of a group being linked to another through common element.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3021,22 +3021,22 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Since no L is M and some L are K, some J may not be M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>All pens are tools. Some tools are pencils. Are some pens pencils?</t>
+          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>No direct relation between pens and pencils.</t>
+          <t>No info.</t>
         </is>
       </c>
     </row>
@@ -3112,66 +3112,66 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>No birds are mammals. All mammals breathe air. Are no birds breathe air?</t>
+          <t>No pen is marker. All markers are tools. Conclusions: I. Some pens are not tools. II. No marker is pen.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>No info on birds and breathing.</t>
+          <t>Negative statement from given facts.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>All mangoes are fruits. No fruit is vegetable. Conclusion?</t>
+          <t>Some boys are students. All students are intelligent. What follows?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Some mangoes are vegetables</t>
+          <t>All boys are intelligent</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>All mangoes are vegetables</t>
+          <t>Some boys are intelligent</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>No mango is vegetable</t>
+          <t>All intelligent are students</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3181,37 +3181,37 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No mango is vegetable</t>
+          <t>Some boys are intelligent</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>All mangoes → fruits, and no fruit → vegetable</t>
+          <t>Some boys → students → intelligent</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Some computers are laptops. All laptops are devices. Conclusion?</t>
+          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Some computers are devices</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>All computers are devices</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>All devices are laptops</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3221,62 +3221,62 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Some computers are devices</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Some computers → laptops → devices</t>
+          <t>No direct info.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Some doctors are rich. All rich people are happy. Are some doctors happy?</t>
+          <t>All pens are books. Some books are papers. Conclusions: I. Some pens are papers. II. All books are pens.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Some doctors are rich and rich people are happy.</t>
+          <t>You cannot conclude direct relation unless explicitly stated.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are living beings. Conclusions: I. Some cats are living beings. II. All living beings are cats.</t>
+          <t>No chair is desk. Some desks are tables. Conclusions: I. No chair is table. II. Some tables are not chairs.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3301,37 +3301,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Cats ⊂ animals ⊂ living beings.</t>
+          <t>Partial exclusion inferred.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>All stars are hot. Some hot things are bright. Conclusion?</t>
+          <t>Some computers are laptops. All laptops are devices. Conclusion?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>All stars are bright</t>
+          <t>Some computers are devices</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Some stars are bright</t>
+          <t>All computers are devices</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Some stars are hot</t>
+          <t>All devices are laptops</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Some stars are hot</t>
+          <t>Some computers are devices</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>All stars → hot</t>
+          <t>Some computers → laptops → devices</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Some P are Q. No Q is R. Are some P not R?</t>
+          <t>No P is Q. All Q are R. Some R are S. Are some P not S?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3381,22 +3381,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>No Q is R, so some P not R.</t>
+          <t>Cannot conclude about P and S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Some M are N. No N is O. All O are P. Are some M not P?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3432,11 +3432,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Some fruits are sweet. All sweets are tasty. Are some fruits tasty?</t>
+          <t>No dogs are cats. All cats are pets. Are no dogs pets?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3461,62 +3461,62 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Some fruits are sweet and sweets are tasty.</t>
+          <t>No info on dogs and pets.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Some students are hardworking. All hardworking people achieve success. Do some students achieve success?</t>
+          <t>Some pencils are red. No red is blue. Conclusions: I. No pencil is blue. II. Some pencils are not blue.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Some students are hardworking who achieve success.</t>
+          <t>Some pencils overlap red, which ≠ blue.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>All poets are writers. Some writers are artists. Conclusions: I. Some poets are artists. II. All poets are artists.</t>
+          <t>All roses are flowers. Some flowers are red. Conclusions: I. Some roses are red. II. All red things are flowers.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3546,72 +3546,72 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Writers ≠ artists by default.</t>
+          <t>Overlap cannot be confirmed.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>No train is plane. All planes are fast. Conclusions: I. No train is fast. II. Some fast are planes.</t>
+          <t>All dogs are animals. All animals are living beings. What can we conclude?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All dogs are living beings</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All living beings are dogs</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some animals are not dogs</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All dogs are living beings</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Statement I overextends logic.</t>
+          <t>A → B → C means A → C</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Some teachers are strict. All strict people are effective. Are some teachers effective?</t>
+          <t>All roses are flowers. No flower is tree. Conclusion?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some roses are trees</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No rose is tree</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All trees are flowers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3621,62 +3621,62 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No rose is tree</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Some teachers are strict and strict people are effective.</t>
+          <t>All roses → flowers, and no flower → tree</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Some trees are tall. All tall things cast shadows. Are some trees casting shadows?</t>
+          <t>Some apples are fruits. All fruits are juicy. Conclusions: I. Some apples are juicy. II. All juicy things are fruits.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Some trees are tall and tall things cast shadows.</t>
+          <t>Partial overlap with juicy items.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>No flowers are trees. Some trees are plants. Are some flowers plants?</t>
+          <t>Some books are novels. All novels are stories. Are some books stories?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>No direct relation given between flowers and plants.</t>
+          <t>Some books belong to novels which are stories.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>No books are papers. All papers are white. Are no books white?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>No info on books and white.</t>
         </is>
       </c>
     </row>
@@ -3756,22 +3756,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All birds are animals. Some animals are flying. Conclusion?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some birds are flying</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All animals are birds</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All birds are flying</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3781,102 +3781,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some birds are flying</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Some Z not X implies some Y not X.</t>
+          <t>All birds → animals → some flying</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Some men are doctors. All doctors help people. Do some men help people?</t>
+          <t>No pen is pencil. All pencils are blue. Conclusion?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some pens are blue</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No pen is blue</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All blue are pencils</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Some men are doctors who help people.</t>
+          <t>No connection between pen and blue</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>All kings are rulers. No ruler is weak. Conclusions: I. No king is weak. II. All weak are kings.</t>
+          <t>No table is chair. All chairs are wooden. Conclusion?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some tables are wooden</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No table is wooden</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>No chair is table</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No chair is table</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Exclusive trait of group extends to all members.</t>
+          <t>No table → chair = No chair → table</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Some fruits are mangoes. All mangoes are yellow. Conclusions: I. Some fruits are yellow. II. All fruits are mangoes.</t>
+          <t>Some pens are pencils. All pencils are erasers. Conclusions: I. Some pens are erasers. II. All erasers are pencils.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3906,32 +3906,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Through mangoes, yellow connection inferred.</t>
+          <t>Some pens overlap with erasers due to common pencils.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>No cats are dogs. All dogs are animals. Are no cats animals?</t>
+          <t>No lion is a deer. Some deer are animals. Conclusion?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No lion is an animal</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some lions are deer</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No deer is lion</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3941,22 +3941,22 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No deer is lion</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>No info on cats and animals.</t>
+          <t>No lion → deer = No deer → lion</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Some men are honest. All honest people are respected. Are some men respected?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3981,37 +3981,37 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Some men are honest and honest people are respected.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
+          <t>All stars are hot. Some hot things are bright. Conclusion?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All stars are bright</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some stars are bright</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some stars are hot</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4021,62 +4021,62 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some stars are hot</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>No direct info.</t>
+          <t>All stars → hot</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>All roses are flowers. No flower is tree. Conclusion?</t>
+          <t>Some keys are locks. Some locks are doors. Conclusions: I. Some keys are doors. II. All keys are doors.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Some roses are trees</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No rose is tree</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>All trees are flowers</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>No rose is tree</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>All roses → flowers, and no flower → tree</t>
+          <t>No definite connection between keys and doors.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Some cars are fast. All fast things are expensive. Are some cars expensive?</t>
+          <t>All lions are animals. Some animals are wild. Are all lions wild?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4101,22 +4101,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Some cars are fast and fast things are expensive.</t>
+          <t>Only some animals are wild.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Some students are intelligent. All intelligent people succeed. Do some students succeed?</t>
+          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4146,57 +4146,57 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Some students are intelligent who succeed.</t>
+          <t>No H is I, so some F not I.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>All cars are vehicles. All trucks are vehicles. Conclusions: I. Some trucks are cars. II. All cars are trucks.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Common class doesn’t mean crossover between groups.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>No chairs are tables. All tables are furniture. Are no chairs furniture?</t>
+          <t>All pens are tools. Some tools are pencils. Are some pens pencils?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No info about chairs and furniture.</t>
+          <t>No direct relation between pens and pencils.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>All flowers are plants. Some plants are green. Conclusions: I. All flowers are green. II. Some flowers are green.</t>
+          <t>Some cups are plates. All plates are spoons. Conclusions: I. Some cups are spoons. II. All spoons are cups.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4261,22 +4261,22 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Cannot determine specific intersection from partial.</t>
+          <t>Some indirect overlap is inferred.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>All birds have feathers. Some birds are colorful. Are some colorful things having feathers?</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4301,77 +4301,77 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>No direct info on colorful things and feathers.</t>
+          <t>No V is W, so some T are not W.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>No bats are birds. All birds can fly. Are no bats able to fly?</t>
+          <t>All pens are pencils. No pencil is marker. Conclusions: I. No pen is marker. II. Some markers are pens.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>No info on bats' flying ability here.</t>
+          <t>Transitive exclusion applies.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Some cats are black. All black are wild. Conclusion?</t>
+          <t>Some teachers are strict. All strict people are effective. Are some teachers effective?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Some cats are wild</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>All cats are wild</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Some black are cats</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Some cats are wild</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Some cats → black → wild</t>
+          <t>Some teachers are strict and strict people are effective.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>No F is G. All G are H. Some H are I. Are some F not I?</t>
+          <t>Some M are N. No N is O. All O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4426,97 +4426,97 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>No direct info on F and I.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>No fish are birds. All birds have wings. Are no fish have wings?</t>
+          <t>All flowers are plants. Some plants are green. Conclusions: I. All flowers are green. II. Some flowers are green.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>No info on fish and wings.</t>
+          <t>Cannot determine specific intersection from partial.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>All engineers are professionals. Some professionals are teachers. Conclusions: I. Some engineers are teachers. II. All engineers are teachers.</t>
+          <t>All mangoes are fruits. No fruit is vegetable. Conclusion?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some mangoes are vegetables</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All mangoes are vegetables</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>No mango is vegetable</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>No mango is vegetable</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Overlap can’t be assumed.</t>
+          <t>All mangoes → fruits, and no fruit → vegetable</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>All A are B. Some C are not B. Can some C be A?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Since some C are not B, some C might or might not be A.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>All birds can fly. Some birds are colorful. Are some colorful things flying?</t>
+          <t>No flowers are trees. Some trees are plants. Are some flowers plants?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4586,32 +4586,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>No direct info on colorful things and flying.</t>
+          <t>No direct relation given between flowers and plants.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Some birds are parrots. All parrots are green. What can we say?</t>
+          <t>No cats are dogs. All dogs are animals. Are no cats animals?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Some birds are green</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>All green are parrots</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Some parrots are birds</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4621,22 +4621,22 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Some parrots are birds</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Some birds → parrots</t>
+          <t>No info on cats and animals.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Some buses are cars. All cars are vehicles. Conclusions: I. Some buses are vehicles. II. All vehicles are buses.</t>
+          <t>All lions are wild. No wild is pet. Conclusions: I. No lion is pet. II. Some lions are pets.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Transitive link holds.</t>
+          <t>Categorical exclusion carries to subset.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>No students are lazy. Some lazy people are careless. Are no students careless?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4706,57 +4706,57 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>No info on students and careless.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Some chairs are tables. All tables are wood. Conclusions: I. Some chairs are wood. II. All wood are tables.</t>
+          <t>Some books are novels. All novels are fiction. Conclusion?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some books are fiction</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All books are fiction</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All fiction are novels</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some books are fiction</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>'Some' does not imply full connection unless supported.</t>
+          <t>Some books → novels → fiction</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>All roses are flowers. Some flowers are fragrant. Are all roses fragrant?</t>
+          <t>Some birds are flying creatures. All flying creatures can fly. Can some birds fly?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Only some flowers are fragrant, no info if roses are.</t>
+          <t>Some birds belong to flying creatures which can fly.</t>
         </is>
       </c>
     </row>
@@ -4796,102 +4796,102 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>No cars are bicycles. Some bicycles are two-wheelers. Are no cars two-wheelers?</t>
+          <t>All goats are mammals. All mammals are animals. Conclusions: I. All goats are animals. II. All animals are goats.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>No info on cars and two-wheelers.</t>
+          <t>Proper direction of deduction matters.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>All pens are books. Some books are papers. Conclusions: I. Some pens are papers. II. All books are pens.</t>
+          <t>No cars are bikes. All bikes are fast. Are no cars fast?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>You cannot conclude direct relation unless explicitly stated.</t>
+          <t>No info on cars and fast relation.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>All rivers are water bodies. Some water bodies are dirty. Are some rivers dirty?</t>
+          <t>No fish is bird. All birds can fly. Conclusion?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No fish can fly</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All fish are birds</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some fish can fly</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4901,22 +4901,22 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No fish can fly</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>No direct info on rivers and dirty.</t>
+          <t>No fish → bird → fly</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
+          <t>No pencils are erasers. All erasers are stationery. Are no pencils stationery?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4941,62 +4941,62 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Because no Z is W, and some Y are Z, some X may not be W.</t>
+          <t>No info on pencils and stationery relation.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Some pencils are red. No red is blue. Conclusions: I. No pencil is blue. II. Some pencils are not blue.</t>
+          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Some pencils overlap red, which ≠ blue.</t>
+          <t>No R is S, so some P not S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Some birds are flying creatures. All flying creatures can fly. Can some birds fly?</t>
+          <t>All cars are vehicles. Some vehicles are expensive. Are all cars expensive?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5021,102 +5021,102 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Some birds belong to flying creatures which can fly.</t>
+          <t>Some vehicles are expensive, cars may or may not be expensive.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Some mobiles are gadgets. All gadgets are expensive. Conclusions: I. Some mobiles are expensive. II. All mobiles are gadgets.</t>
+          <t>No A is B. All B are C. Some C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Indirect connection possible for subset.</t>
+          <t>No direct link between A and D.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Some birds are parrots. Some parrots are green. Conclusions: I. Some birds are green. II. Some green are parrots.</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Direct overlap of some parrots and green.</t>
+          <t>Because some Z are not X, and some Y are Z, some Y may not be X.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
+          <t>No X is Y. All Y are Z. Are some Z not X?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>No direct conclusion.</t>
+          <t>Since no X is Y and all Y are Z, some Z are not X.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Some P are Q. No Q is R. Are some P not R?</t>
+          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5181,22 +5181,22 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Since no Q is R, some P may not be R.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>No pencils are erasers. All erasers are stationery. Are no pencils stationery?</t>
+          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5221,222 +5221,222 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>No info on pencils and stationery relation.</t>
+          <t>No R is S, so some P not S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Some dogs are cats. No cat is rabbit. Conclusions: I. Some dogs are rabbits. II. No dog is rabbit.</t>
+          <t>No S is T. Some T are U. All U are V. Are some S not V?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Insufficient link between groups.</t>
+          <t>No S is T, so some S not V.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>No cats are mice. All mice are small. Are no cats small?</t>
+          <t>Some fruits are mangoes. All mangoes are yellow. Conclusions: I. Some fruits are yellow. II. All fruits are mangoes.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>No info on cats and small.</t>
+          <t>Through mangoes, yellow connection inferred.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>No doctors are lawyers. Some lawyers are teachers. Are some doctors teachers?</t>
+          <t>No bird is insect. All parrots are birds. Conclusions: I. No parrot is insect. II. Some insects are birds.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>No direct relation between doctors and teachers.</t>
+          <t>Parrot subset inherits bird restriction.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Some boys are girls. Some girls are intelligent. Conclusions: I. Some boys are intelligent. II. All boys are intelligent.</t>
+          <t>All rivers are water bodies. Some water bodies are dirty. Are some rivers dirty?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>No definite relation proven across categories.</t>
+          <t>No direct info on rivers and dirty.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Some cups are plates. All plates are spoons. Conclusions: I. Some cups are spoons. II. All spoons are cups.</t>
+          <t>No dogs are cats. All cats are animals. Are no dogs animals?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Some indirect overlap is inferred.</t>
+          <t>We cannot conclude about dogs being animals.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
+          <t>Some cars are fast. All fast things are expensive. Are some cars expensive?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5461,22 +5461,22 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Some cars are fast and fast things are expensive.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>All goats are mammals. All mammals are animals. Conclusions: I. All goats are animals. II. All animals are goats.</t>
+          <t>All cows are animals. All animals are herbivores. Conclusions: I. Some cows are herbivores. II. All cows are herbivores.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5501,37 +5501,37 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Proper direction of deduction matters.</t>
+          <t>Cows ⊂ animals ⊂ herbivores.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>No tree is stone. Some stones are heavy. Conclusion?</t>
+          <t>No bats are birds. All birds can fly. Are no bats able to fly?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No tree is heavy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Some trees are heavy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>All stones are trees</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5541,102 +5541,102 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>No connection between tree and heavy</t>
+          <t>No info on bats' flying ability here.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>No train is plane. All planes are fast. Conclusions: I. No train is fast. II. Some fast are planes.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Because some Z are not X, and some Y are Z, some Y may not be X.</t>
+          <t>Statement I overextends logic.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
+          <t>All boys are students. Some students are girls. Conclusions: I. Some boys are girls. II. All girls are students.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>No H is I, so some F not I.</t>
+          <t>Some students are girls, so some girls are students.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>All students are learners. Some learners are athletes. Are some students athletes?</t>
+          <t>All cars are vehicles. Some vehicles are fast. Are all cars fast?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>No direct info on students and athletes.</t>
+          <t>Only some vehicles are fast, no info about cars.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Some boys are students. All students study. Do some boys study?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5701,22 +5701,22 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Some boys belong to students who study.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Some flowers are red. All red things are attractive. Are some flowers attractive?</t>
+          <t>No cars are bicycles. Some bicycles are two-wheelers. Are no cars two-wheelers?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5741,22 +5741,22 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Some flowers are red and red things are attractive.</t>
+          <t>No info on cars and two-wheelers.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are mammals. Conclusions: I. All cats are mammals. II. All mammals are cats.</t>
+          <t>Some boys are singers. All singers are dancers. Conclusions: I. Some boys are dancers. II. All dancers are boys.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>None follow</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>All members of first category are also members of the final category.</t>
+          <t>Some boys overlap dancers via singers.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>No apple is orange. All oranges are juicy. Conclusion?</t>
+          <t>No fish are birds. All birds have wings. Are no fish have wings?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No apple is juicy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Some apples are juicy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>All apples are oranges</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>No link between apple and juicy</t>
+          <t>No info on fish and wings.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>Some doctors are rich. All rich people are happy. Are some doctors happy?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5866,17 +5866,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>No V is W, so some T not W.</t>
+          <t>Some doctors are rich and rich people are happy.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>All cats are animals. All animals are living beings. Are all cats living beings?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5901,197 +5901,197 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>If all cats are animals and all animals are living beings, all cats are living beings.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>All actors are performers. No performer is lazy. Conclusions: I. No actor is lazy. II. Some lazy are actors.</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Subset retains universal trait.</t>
+          <t>No V is W, so some T not W.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Some boys are singers. All singers are dancers. Conclusions: I. Some boys are dancers. II. All dancers are boys.</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Some boys overlap dancers via singers.</t>
+          <t>No conclusive relation between M and P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>All dogs are animals. Some animals are cats. Conclusions: I. Some dogs are cats. II. All animals are dogs.</t>
+          <t>Some birds are parrots. All parrots are green. What can we say?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some birds are green</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All green are parrots</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some parrots are birds</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some parrots are birds</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Only the conclusions logically follow based on statements.</t>
+          <t>Some birds → parrots</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>All pens are objects. Some objects are useful. Conclusion?</t>
+          <t>Some mobiles are gadgets. All gadgets are expensive. Conclusions: I. Some mobiles are expensive. II. All mobiles are gadgets.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Some pens are useful</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>All useful are pens</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Some objects are pens</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Some objects are pens</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>All pens → objects</t>
+          <t>Indirect connection possible for subset.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Some chairs are wooden. All wooden are brown. Conclusion?</t>
+          <t>No cats are mice. All mice are small. Are no cats small?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>All chairs are brown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Some chairs are brown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Some wooden are chairs</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6101,62 +6101,62 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Some chairs are brown</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Some chairs → wooden → brown</t>
+          <t>No info on cats and small.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Some girls are dancers. All dancers are flexible. Conclusion?</t>
+          <t>All roses are red. Some red things are beautiful. Conclusions: I. Some roses are beautiful. II. All red things are roses.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>All girls are flexible</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Some dancers are girls</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Some girls are flexible</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>All flexible are girls</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Some girls are flexible</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Some girls → dancers → flexible</t>
+          <t>Common trait not confirmed for subset.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>No birds are mammals. All mammals breathe air. Are no birds breathe air?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6186,32 +6186,32 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>No conclusive relation.</t>
+          <t>No info on birds and breathing.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>No M is N. Some N are O. All O are P. Are some M not P?</t>
+          <t>Some chairs are wooden. All wooden are brown. Conclusion?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All chairs are brown</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some chairs are brown</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some wooden are chairs</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6221,22 +6221,22 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some chairs are brown</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>No conclusive data.</t>
+          <t>Some chairs → wooden → brown</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>No apple is banana. Some bananas are yellow. Conclusions: I. Some apples are yellow. II. No apple is yellow.</t>
+          <t>All stones are rocks. Some rocks are heavy. Conclusions: I. Some stones are heavy. II. All heavy are rocks.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6266,32 +6266,32 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>No definite apple-yellow link.</t>
+          <t>Overlap is not definite.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>All birds are animals. Some animals are flying. Conclusion?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Some birds are flying</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>All animals are birds</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>All birds are flying</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6301,37 +6301,37 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Some birds are flying</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>All birds → animals → some flying</t>
+          <t>Because some Z not X, some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
+          <t>Some toys are plastic. All plastic is harmful. Conclusion?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some toys are harmful</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All toys are harmful</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some harmful are toys</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some toys are harmful</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Since no L is M and some L are K, some J may not be M.</t>
+          <t>Some toys → plastic → harmful</t>
         </is>
       </c>
     </row>
@@ -6356,87 +6356,87 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
+          <t>Some dogs are cats. No cat is rabbit. Conclusions: I. Some dogs are rabbits. II. No dog is rabbit.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>No info.</t>
+          <t>Insufficient link between groups.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Some pens are pencils. All pencils are erasers. Conclusions: I. Some pens are erasers. II. All erasers are pencils.</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Some pens overlap with erasers due to common pencils.</t>
+          <t>No direct conclusion can be drawn about A and D.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>No X is Y. All Y are Z. Are some Z not X?</t>
+          <t>Some fruits are sweet. All sweets are tasty. Are some fruits tasty?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6466,97 +6466,97 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Since no X is Y and all Y are Z, some Z are not X.</t>
+          <t>Some fruits are sweet and sweets are tasty.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>Some mangoes are sweet. All sweet things are healthy. Conclusions: I. Some mangoes are healthy. II. All mangoes are healthy.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>No V is W, so some T not W.</t>
+          <t>Indirect conclusion from overlap.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>All flowers are plants. Some plants are medicinal. Are all flowers medicinal?</t>
+          <t>All kids are students. No student is teacher. Conclusions: I. No kid is teacher. II. Some teachers are students.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Only some plants are medicinal.</t>
+          <t>Exclusion travels to subgroup.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are red. Are some apples red?</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6581,62 +6581,62 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>No direct info on apples and red.</t>
+          <t>Since no V is W, some T which are U and U are V, are not W.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>All dogs are animals. All animals are living beings. What can we conclude?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>All dogs are living beings</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>All living beings are dogs</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Some animals are not dogs</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>All dogs are living beings</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>A → B → C means A → C</t>
+          <t>No conclusive relation.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>All M are N. Some N are O. No O is P. Are some M not P?</t>
+          <t>All birds can fly. Some birds are colorful. Are some colorful things flying?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6661,142 +6661,142 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Some M could belong to N which belong to O; none O is P, so some M are not P.</t>
+          <t>No direct info on colorful things and flying.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Some tables are chairs. No chair is sofa. Conclusions: I. Some tables are not sofas. II. No table is sofa.</t>
+          <t>No books are newspapers. Some newspapers are daily. Are no books daily?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>We know chairs ≠ sofa; table partially overlaps.</t>
+          <t>No info on books being daily.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
+          <t>Some chairs are tables. All tables are wood. Conclusions: I. Some chairs are wood. II. All wood are tables.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Because no Z is W and some Y are Z, some X may not be W.</t>
+          <t>'Some' does not imply full connection unless supported.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>All roses are red. Some red things are beautiful. Conclusions: I. Some roses are beautiful. II. All red things are roses.</t>
+          <t>Some boys are tall. All tall people are strong. Are some boys strong?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Common trait not confirmed for subset.</t>
+          <t>Some boys are tall and tall people are strong.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Some boys are tall. All tall people are strong. Are some boys strong?</t>
+          <t>All apples are fruits. Some fruits are red. Are some apples red?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6821,37 +6821,37 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Some boys are tall and tall people are strong.</t>
+          <t>No direct info on apples and red.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Some books are novels. All novels are fiction. Conclusion?</t>
+          <t>All students are learners. Some learners are athletes. Are some students athletes?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Some books are fiction</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>All books are fiction</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>All fiction are novels</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6861,22 +6861,22 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Some books are fiction</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Some books → novels → fiction</t>
+          <t>No direct info on students and athletes.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>No dogs are cats. All cats are animals. Are no dogs animals?</t>
+          <t>Some K are L. Some L are M. No M is N. Are some K not N?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6906,17 +6906,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>We cannot conclude about dogs being animals.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>All J are K. Some K are L. No L is M. Are some J not M?</t>
+          <t>Some P are Q. No Q is R. Are some P not R?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Since no L is M, some J not M.</t>
+          <t>No Q is R, so some P not R.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>All pens are pencils. No pencil is marker. Conclusions: I. No pen is marker. II. Some markers are pens.</t>
+          <t>No bird is mammal. All mammals are warm-blooded. Conclusions: I. No bird is warm-blooded. II. Some warm-blooded are mammals.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6981,37 +6981,37 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Transitive exclusion applies.</t>
+          <t>All mammals ⊂ warm-blooded, so II true.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Some K are L. Some L are M. No M is N. Are some K not N?</t>
+          <t>Some cats are black. All black are wild. Conclusion?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some cats are wild</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All cats are wild</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some black are cats</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7021,62 +7021,62 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some cats are wild</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some cats → black → wild</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>No pen is pencil. All pencils are blue. Conclusion?</t>
+          <t>All flowers are beautiful. Some beautiful things are expensive. Are some flowers expensive?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Some pens are blue</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>No pen is blue</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>All blue are pencils</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>No connection between pen and blue</t>
+          <t>No direct info about flowers and expensive.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
+          <t>Some cars are red. All red things are bright. Are some cars bright?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7106,32 +7106,32 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>No R is S, so some P not S.</t>
+          <t>Some cars are red and red things are bright.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>No dogs are cats. All cats are pets. Are no dogs pets?</t>
+          <t>No apple is orange. All oranges are juicy. Conclusion?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No apple is juicy</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some apples are juicy</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All apples are oranges</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7141,37 +7141,37 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>No info on dogs and pets.</t>
+          <t>No link between apple and juicy</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Some teachers are writers. All writers are creative. Conclusion?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Some teachers are creative</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>All teachers are creative</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Some creative are teachers</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Some teachers are creative</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Some teachers → writers → creative</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>No M is N. Some N are O. All O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7226,137 +7226,137 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>No conclusive data.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>All cats are animals. All animals are living beings. Conclusions: I. Some cats are living beings. II. All living beings are cats.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>No conclusive relation between M and P.</t>
+          <t>Cats ⊂ animals ⊂ living beings.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are living beings. Are all cats living beings?</t>
+          <t>Some books are pens. Some pens are colors. Conclusions: I. Some books are colors. II. All colors are pens.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>If all cats are animals and all animals are living beings, all cats are living beings.</t>
+          <t>Indirect link not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
+          <t>All dogs are animals. Some animals are cats. Conclusions: I. Some dogs are cats. II. All animals are dogs.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Because no H is I, some F not I.</t>
+          <t>Only the conclusions logically follow based on statements.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>All boys are students. Some students are girls. Conclusions: I. Some boys are girls. II. All girls are students.</t>
+          <t>All kings are rulers. No ruler is weak. Conclusions: I. No king is weak. II. All weak are kings.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7381,62 +7381,62 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Some students are girls, so some girls are students.</t>
+          <t>Exclusive trait of group extends to all members.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>No books are newspapers. Some newspapers are daily. Are no books daily?</t>
+          <t>All squares are rectangles. All rectangles are shapes. Conclusions: I. All squares are shapes. II. Some shapes are squares.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>No info on books being daily.</t>
+          <t>Multiple logical links proven.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Some fruits are apples. All apples are red. Are some fruits red?</t>
+          <t>No doctors are lawyers. Some lawyers are teachers. Are some doctors teachers?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>If some fruits are apples and apples are red, some fruits are red.</t>
+          <t>No direct relation between doctors and teachers.</t>
         </is>
       </c>
     </row>

--- a/Data/Sylogism.xlsx
+++ b/Data/Sylogism.xlsx
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some flowers are red. All red things are attractive. Are some flowers attractive?</t>
+          <t>All roses are flowers. Some flowers are fragrant. Are all roses fragrant?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,37 +501,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Some flowers are red and red things are attractive.</t>
+          <t>Only some flowers are fragrant, no info if roses are.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
+          <t>Some computers are laptops. All laptops are devices. Conclusion?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some computers are devices</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All computers are devices</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All devices are laptops</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,62 +541,62 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some computers are devices</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Some computers → laptops → devices</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some boys are girls. Some girls are intelligent. Conclusions: I. Some boys are intelligent. II. All boys are intelligent.</t>
+          <t>Some girls are dancers. All dancers are flexible. Conclusion?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All girls are flexible</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some dancers are girls</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some girls are flexible</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>All flexible are girls</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some girls are flexible</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No definite relation proven across categories.</t>
+          <t>Some girls → dancers → flexible</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No D is E. Some F are D. All F are G. Are some G not E?</t>
+          <t>All birds have feathers. Some birds are colorful. Are some colorful things having feathers?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -621,62 +621,62 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Since no D is E and some F are D, some G (which include F) are not E.</t>
+          <t>No direct info on colorful things and feathers.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>All poets are writers. Some writers are artists. Conclusions: I. Some poets are artists. II. All poets are artists.</t>
+          <t>No cars are bicycles. Some bicycles are two-wheelers. Are no cars two-wheelers?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Writers ≠ artists by default.</t>
+          <t>No info on cars and two-wheelers.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>All pens are useful. Some useful things are costly. Are some pens costly?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No direct info on pens and costly.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>No tree is stone. Some stones are heavy. Conclusion?</t>
+          <t>Some trees are tall. All tall things cast shadows. Are some trees casting shadows?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No tree is heavy</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Some trees are heavy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>All stones are trees</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No connection between tree and heavy</t>
+          <t>Some trees are tall and tall things cast shadows.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Some buses are cars. All cars are vehicles. Conclusions: I. Some buses are vehicles. II. All vehicles are buses.</t>
+          <t>Some teachers are writers. All writers are creative. Conclusion?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some teachers are creative</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All teachers are creative</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some creative are teachers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some teachers are creative</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Transitive link holds.</t>
+          <t>Some teachers → writers → creative</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>All roses are flowers. Some flowers are fragrant. Are all roses fragrant?</t>
+          <t>All pens are books. Some books are papers. Conclusions: I. Some pens are papers. II. All books are pens.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Only some flowers are fragrant, no info if roses are.</t>
+          <t>You cannot conclude direct relation unless explicitly stated.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>No cats are mice. All mice are small. Are no cats small?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Because some Z not X, some Y not X.</t>
+          <t>No info on cats and small.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Some trees are tall. All tall things cast shadows. Are some trees casting shadows?</t>
+          <t>No pencils are erasers. All erasers are stationery. Are no pencils stationery?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -901,102 +901,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Some trees are tall and tall things cast shadows.</t>
+          <t>No info on pencils and stationery relation.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are sweet. What follows?</t>
+          <t>No S is R. Some R are Q. All Q are P. Are some P not S?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Some apples are sweet</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>All sweet are fruits</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Some fruits are apples</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>All apples are sweet</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Some fruits are apples</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>All apples → fruits, so some fruits ← apples</t>
+          <t>Since no S is R, some P which are Q and R are not S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>All engineers are professionals. Some professionals are teachers. Conclusions: I. Some engineers are teachers. II. All engineers are teachers.</t>
+          <t>All flowers are beautiful. Some beautiful things are expensive. Are some flowers expensive?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Overlap can’t be assumed.</t>
+          <t>No direct info about flowers and expensive.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1021,77 +1021,77 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No L is M, so some J not M.</t>
+          <t>No conclusive relation between M and P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All lions are wild. No wild is pet. Conclusions: I. No lion is pet. II. Some lions are pets.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Some Z not X implies some Y not X.</t>
+          <t>Categorical exclusion carries to subset.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>No students are lazy. Some lazy people are careless. Are no students careless?</t>
+          <t>Some cats are black. All black are wild. Conclusion?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some cats are wild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All cats are wild</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some black are cats</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some cats are wild</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No info on students and careless.</t>
+          <t>Some cats → black → wild</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>No chairs are tables. All tables are furniture. Are no chairs furniture?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1146,57 +1146,57 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No info about chairs and furniture.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>All birds have feathers. Some birds are colorful. Are some colorful things having feathers?</t>
+          <t>Some cups are plates. All plates are spoons. Conclusions: I. Some cups are spoons. II. All spoons are cups.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No direct info on colorful things and feathers.</t>
+          <t>Some indirect overlap is inferred.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>All men are humans. Some humans are kind. Conclusions: I. Some men are kind. II. All men are kind.</t>
+          <t>All poets are writers. Some writers are artists. Conclusions: I. Some poets are artists. II. All poets are artists.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Some does not apply across unless proven.</t>
+          <t>Writers ≠ artists by default.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>All A are B. Some C are not B. Can some C be A?</t>
+          <t>Some doctors are rich. All rich people are happy. Are some doctors happy?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1261,62 +1261,62 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Since some C are not B, some C might or might not be A.</t>
+          <t>Some doctors are rich and rich people are happy.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Some girls are dancers. All dancers are flexible. Conclusion?</t>
+          <t>No chairs are tables. All tables are furniture. Are no chairs furniture?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>All girls are flexible</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Some dancers are girls</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Some girls are flexible</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>All flexible are girls</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Some girls are flexible</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Some girls → dancers → flexible</t>
+          <t>No info about chairs and furniture.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Some men are honest. All honest people are respected. Are some men respected?</t>
+          <t>Some cars are fast. All fast things are expensive. Are some cars expensive?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Some men are honest and honest people are respected.</t>
+          <t>Some cars are fast and fast things are expensive.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are mammals. Conclusions: I. All cats are mammals. II. All mammals are cats.</t>
+          <t>Some teachers are doctors. All doctors are professionals. Conclusions: I. Some teachers are professionals. II. All professionals are doctors.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>None follow</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1386,32 +1386,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>All members of first category are also members of the final category.</t>
+          <t>Partial link via doctors.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>All bats are mammals. Some mammals are nocturnal. Conclusion?</t>
+          <t>Some birds are parrots. All parrots are green. What can we say?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Some bats are nocturnal</t>
+          <t>Some birds are green</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>All bats are nocturnal</t>
+          <t>All green are parrots</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Some mammals are bats</t>
+          <t>Some parrots are birds</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Some mammals are bats</t>
+          <t>Some parrots are birds</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>All bats → mammals</t>
+          <t>Some birds → parrots</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are sour. Are some apples sour?</t>
+          <t>No F is G. All G are H. Some H are I. Are some F not I?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No info on apples being sour.</t>
+          <t>No direct info on F and I.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Some teachers are writers. All writers are creative. Conclusion?</t>
+          <t>No X is Y. All Y are Z. Are some Z not X?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Some teachers are creative</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>All teachers are creative</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Some creative are teachers</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Some teachers are creative</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Some teachers → writers → creative</t>
+          <t>Since no X is Y and all Y are Z, some Z are not X.</t>
         </is>
       </c>
     </row>
@@ -1516,127 +1516,127 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Some tables are chairs. No chair is sofa. Conclusions: I. Some tables are not sofas. II. No table is sofa.</t>
+          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>We know chairs ≠ sofa; table partially overlaps.</t>
+          <t>No R is S, so some P not S.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>All lions are animals. No animal is plant. Conclusions: I. No lion is plant. II. All lions are plants.</t>
+          <t>Some books are novels. All novels are fiction. Conclusion?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some books are fiction</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All books are fiction</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All fiction are novels</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some books are fiction</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lions ⊂ animals, animals ≠ plants.</t>
+          <t>Some books → novels → fiction</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Some men are doctors. All doctors help people. Do some men help people?</t>
+          <t>Some books are pens. Some pens are colors. Conclusions: I. Some books are colors. II. All colors are pens.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Some men are doctors who help people.</t>
+          <t>Indirect link not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>All mountains are high. Some high places are cold. Are all mountains cold?</t>
+          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1661,102 +1661,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Partial overlap between high and cold places.</t>
+          <t>No L is M, so some J not M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>All flowers are plants. Some plants are medicinal. Are all flowers medicinal?</t>
+          <t>Some apples are fruits. All fruits are juicy. Conclusions: I. Some apples are juicy. II. All juicy things are fruits.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Only some plants are medicinal.</t>
+          <t>Partial overlap with juicy items.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
+          <t>All dogs are loyal. No loyal being is dishonest. Conclusions: I. No dog is dishonest. II. All dishonest are dogs.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Because no H is I, some F not I.</t>
+          <t>No and "All" combined can show exclusivity.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
+          <t>Some books are novels. All novels are stories. Are some books stories?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>No conclusive data.</t>
+          <t>Some books belong to novels which are stories.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
+          <t>All M are N. Some N are O. No O is P. Are some M not P?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1821,22 +1821,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some M could belong to N which belong to O; none O is P, so some M are not P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
+          <t>Some boys are students. All students study. Do some boys study?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1861,22 +1861,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No direct conclusion.</t>
+          <t>Some boys belong to students who study.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Some students are intelligent. All intelligent people succeed. Do some students succeed?</t>
+          <t>No fish are birds. All birds have wings. Are no fish have wings?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1901,182 +1901,182 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Some students are intelligent who succeed.</t>
+          <t>No info on fish and wings.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Some teachers are doctors. All doctors are professionals. Conclusions: I. Some teachers are professionals. II. All professionals are doctors.</t>
+          <t>All apples are fruits. Some fruits are red. Are some apples red?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Partial link via doctors.</t>
+          <t>No direct info on apples and red.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Some fruits are apples. All apples are red. Are some fruits red?</t>
+          <t>All cats are animals. All animals are living beings. Conclusions: I. Some cats are living beings. II. All living beings are cats.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>If some fruits are apples and apples are red, some fruits are red.</t>
+          <t>Cats ⊂ animals ⊂ living beings.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
+          <t>All men are humans. Some humans are kind. Conclusions: I. Some men are kind. II. All men are kind.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>No conclusive info.</t>
+          <t>Some does not apply across unless proven.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Some birds are parrots. Some parrots are green. Conclusions: I. Some birds are green. II. Some green are parrots.</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Direct overlap of some parrots and green.</t>
+          <t>No conclusion.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>All apples are fruits. No fruit is vegetable. Conclusions: I. No apple is vegetable. II. Some apples are vegetables.</t>
+          <t>All actors are performers. No performer is lazy. Conclusions: I. No actor is lazy. II. Some lazy are actors.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Exclusive property holds.</t>
+          <t>Subset retains universal trait.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>All pens are objects. Some objects are useful. Conclusion?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Some pens are useful</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>All useful are pens</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Some objects are pens</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2141,62 +2141,62 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Some objects are pens</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>All pens → objects</t>
+          <t>No conclusive relation.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>No apple is banana. Some bananas are yellow. Conclusions: I. Some apples are yellow. II. No apple is yellow.</t>
+          <t>All actors are dancers. Some dancers are singers. Can we conclude some actors are singers?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>No definite apple-yellow link.</t>
+          <t>Partial overlap between dancers and singers; actors may or may not be singers.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2221,77 +2221,77 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>No conclusion.</t>
+          <t>Because no Z is W and some Y are Z, some X may not be W.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>All J are K. Some K are L. No L is M. Are some J not M?</t>
+          <t>All cars are vehicles. All trucks are vehicles. Conclusions: I. Some trucks are cars. II. All cars are trucks.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Since no L is M, some J not M.</t>
+          <t>Common class doesn’t mean crossover between groups.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>All actors are dancers. Some dancers are singers. Can we conclude some actors are singers?</t>
+          <t>No fish is bird. All birds can fly. Conclusion?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No fish can fly</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All fish are birds</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some fish can fly</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2301,77 +2301,77 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No fish can fly</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Partial overlap between dancers and singers; actors may or may not be singers.</t>
+          <t>No fish → bird → fly</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>All paper is white. Some white is light. Conclusions: I. Some paper is light. II. All light is white.</t>
+          <t>All birds are animals. Some animals are flying. Conclusion?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some birds are flying</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All animals are birds</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All birds are flying</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some birds are flying</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>No guaranteed overlap shown.</t>
+          <t>All birds → animals → some flying</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Some students are hardworking. All hardworking people achieve success. Do some students achieve success?</t>
+          <t>No apple is orange. All oranges are juicy. Conclusion?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No apple is juicy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some apples are juicy</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All apples are oranges</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2381,62 +2381,62 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Some students are hardworking who achieve success.</t>
+          <t>No link between apple and juicy</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>All M are N. Some N are O. No O is P. Are some M not P?</t>
+          <t>No chair is desk. Some desks are tables. Conclusions: I. No chair is table. II. Some tables are not chairs.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Some M could belong to N which belong to O; none O is P, so some M are not P.</t>
+          <t>Partial exclusion inferred.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>No F is G. All G are H. Some H are I. Are some F not I?</t>
+          <t>No students are lazy. Some lazy people are careless. Are no students careless?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2466,57 +2466,57 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>No direct info on F and I.</t>
+          <t>No info on students and careless.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>All fruits are healthy. Some healthy are tasty. Conclusion?</t>
+          <t>No pen is pencil. All pencils are blue. Conclusion?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Some fruits are tasty</t>
+          <t>Some pens are blue</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>All healthy are fruits</t>
+          <t>No pen is blue</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Some fruits are healthy</t>
+          <t>All blue are pencils</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>All tasty are fruits</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Some fruits are healthy</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>All fruits → healthy</t>
+          <t>No connection between pen and blue</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
+          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2541,22 +2541,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Because no Z is W and some Y are Z, some X may not be W.</t>
+          <t>No info.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>No S is R. Some R are Q. All Q are P. Are some P not S?</t>
+          <t>Some fruits are apples. All apples are red. Are some fruits red?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Since no S is R, some P which are Q and R are not S.</t>
+          <t>If some fruits are apples and apples are red, some fruits are red.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
+          <t>All pens are useful. Some useful things are costly. Are some pens costly?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2621,102 +2621,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Because no Z is W, and some Y are Z, some X may not be W.</t>
+          <t>No direct info on pens and costly.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>All dogs are loyal. No loyal being is dishonest. Conclusions: I. No dog is dishonest. II. All dishonest are dogs.</t>
+          <t>All stars are hot. Some hot things are bright. Conclusion?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All stars are bright</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some stars are bright</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some stars are hot</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some stars are hot</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>No and "All" combined can show exclusivity.</t>
+          <t>All stars → hot</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>All actors are performers. No performer is lazy. Conclusions: I. No actor is lazy. II. Some lazy are actors.</t>
+          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Subset retains universal trait.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>No M is N. Some N are O. All O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2741,157 +2741,157 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No V is W, so some T not W.</t>
+          <t>No conclusive data.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Some P are Q. No Q is R. Are some P not R?</t>
+          <t>No bird is mammal. All mammals are warm-blooded. Conclusions: I. No bird is warm-blooded. II. Some warm-blooded are mammals.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Since no Q is R, some P may not be R.</t>
+          <t>All mammals ⊂ warm-blooded, so II true.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>All windows are doors. Some doors are walls. Conclusions: I. Some windows are walls. II. Some doors are windows.</t>
+          <t>All roses are flowers. No flower is tree. Conclusion?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some roses are trees</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No rose is tree</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All trees are flowers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No rose is tree</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Some doors are windows due to inclusion.</t>
+          <t>All roses → flowers, and no flower → tree</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Some engineers are scientists. No scientist is artist. Are some engineers not artists?</t>
+          <t>No pen is marker. All markers are tools. Conclusions: I. Some pens are not tools. II. No marker is pen.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Engineers partly overlap scientists; scientists exclude artists.</t>
+          <t>Negative statement from given facts.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>All bats are mammals. Some mammals are nocturnal. Conclusion?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some bats are nocturnal</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All bats are nocturnal</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some mammals are bats</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2901,22 +2901,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some mammals are bats</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>All bats → mammals</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Some boys are students. All students study. Do some boys study?</t>
+          <t>Some M are N. No N is O. All O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Some boys belong to students who study.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Some apples are fruits. All fruits are healthy. Conclusions: I. Some apples are healthy. II. All apples are healthy.</t>
+          <t>All windows are doors. Some doors are walls. Conclusions: I. Some windows are walls. II. Some doors are windows.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2981,62 +2981,62 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Part of a group being linked to another through common element.</t>
+          <t>Some doors are windows due to inclusion.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
+          <t>All apples are fruits. No fruit is vegetable. Conclusions: I. No apple is vegetable. II. Some apples are vegetables.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Since no L is M and some L are K, some J may not be M.</t>
+          <t>Exclusive property holds.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
+          <t>All mountains are high. Some high places are cold. Are all mountains cold?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3066,32 +3066,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>No info.</t>
+          <t>Partial overlap between high and cold places.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Some pencils are long. All long things are thin. Conclusion?</t>
+          <t>No A is B. All B are C. Some C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Some pencils are thin</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>All pencils are thin</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Some thin things are pencils</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3101,237 +3101,237 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Some pencils are thin</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Some pencils → long → thin</t>
+          <t>No direct link between A and D.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>No pen is marker. All markers are tools. Conclusions: I. Some pens are not tools. II. No marker is pen.</t>
+          <t>All A are B. Some C are not B. Can some C be A?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Negative statement from given facts.</t>
+          <t>Since some C are not B, some C might or might not be A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Some boys are students. All students are intelligent. What follows?</t>
+          <t>Some keys are locks. Some locks are doors. Conclusions: I. Some keys are doors. II. All keys are doors.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>All boys are intelligent</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Some boys are intelligent</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>All intelligent are students</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Some boys are intelligent</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Some boys → students → intelligent</t>
+          <t>No definite connection between keys and doors.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
+          <t>Some fruits are mangoes. All mangoes are yellow. Conclusions: I. Some fruits are yellow. II. All fruits are mangoes.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>No direct info.</t>
+          <t>Through mangoes, yellow connection inferred.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>All pens are books. Some books are papers. Conclusions: I. Some pens are papers. II. All books are pens.</t>
+          <t>No P is Q. All Q are R. Some R are S. Are some P not S?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>You cannot conclude direct relation unless explicitly stated.</t>
+          <t>Cannot conclude about P and S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>No chair is desk. Some desks are tables. Conclusions: I. No chair is table. II. Some tables are not chairs.</t>
+          <t>Some men are doctors. All doctors help people. Do some men help people?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Partial exclusion inferred.</t>
+          <t>Some men are doctors who help people.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Some computers are laptops. All laptops are devices. Conclusion?</t>
+          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Some computers are devices</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>All computers are devices</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>All devices are laptops</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Some computers are devices</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Some computers → laptops → devices</t>
+          <t>No direct info.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>No P is Q. All Q are R. Some R are S. Are some P not S?</t>
+          <t>No dogs are cats. All cats are animals. Are no dogs animals?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cannot conclude about P and S.</t>
+          <t>We cannot conclude about dogs being animals.</t>
         </is>
       </c>
     </row>
@@ -3396,222 +3396,222 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>All stones are rocks. Some rocks are heavy. Conclusions: I. Some stones are heavy. II. All heavy are rocks.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Overlap is not definite.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>No dogs are cats. All cats are pets. Are no dogs pets?</t>
+          <t>Some pencils are red. No red is blue. Conclusions: I. No pencil is blue. II. Some pencils are not blue.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>No info on dogs and pets.</t>
+          <t>Some pencils overlap red, which ≠ blue.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Some pencils are red. No red is blue. Conclusions: I. No pencil is blue. II. Some pencils are not blue.</t>
+          <t>All X are Y. Some Y are Z. No Z is W. Are some X not W?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Some pencils overlap red, which ≠ blue.</t>
+          <t>Because no Z is W, and some Y are Z, some X may not be W.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>All roses are flowers. Some flowers are red. Conclusions: I. Some roses are red. II. All red things are flowers.</t>
+          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Overlap cannot be confirmed.</t>
+          <t>No direct conclusion.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>All dogs are animals. All animals are living beings. What can we conclude?</t>
+          <t>Some pens are pencils. All pencils are erasers. Conclusions: I. Some pens are erasers. II. All erasers are pencils.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>All dogs are living beings</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>All living beings are dogs</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Some animals are not dogs</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>All dogs are living beings</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>A → B → C means A → C</t>
+          <t>Some pens overlap with erasers due to common pencils.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>All roses are flowers. No flower is tree. Conclusion?</t>
+          <t>Some chairs are wooden. All wooden are brown. Conclusion?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Some roses are trees</t>
+          <t>All chairs are brown</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No rose is tree</t>
+          <t>Some chairs are brown</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>All trees are flowers</t>
+          <t>Some wooden are chairs</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3621,62 +3621,62 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>No rose is tree</t>
+          <t>Some chairs are brown</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>All roses → flowers, and no flower → tree</t>
+          <t>Some chairs → wooden → brown</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Some apples are fruits. All fruits are juicy. Conclusions: I. Some apples are juicy. II. All juicy things are fruits.</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Partial overlap with juicy items.</t>
+          <t>Because some Z are not X, and some Y are Z, some Y may not be X.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Some books are novels. All novels are stories. Are some books stories?</t>
+          <t>All students are learners. Some learners are athletes. Are some students athletes?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3701,77 +3701,77 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Some books belong to novels which are stories.</t>
+          <t>No direct info on students and athletes.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>No books are papers. All papers are white. Are no books white?</t>
+          <t>All roses are flowers. Some flowers are red. Conclusions: I. Some roses are red. II. All red things are flowers.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>No info on books and white.</t>
+          <t>Overlap cannot be confirmed.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>All birds are animals. Some animals are flying. Conclusion?</t>
+          <t>Some students are hardworking. All hardworking people achieve success. Do some students achieve success?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Some birds are flying</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>All animals are birds</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>All birds are flying</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3781,182 +3781,182 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Some birds are flying</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>All birds → animals → some flying</t>
+          <t>Some students are hardworking who achieve success.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>No pen is pencil. All pencils are blue. Conclusion?</t>
+          <t>Some boys are girls. Some girls are intelligent. Conclusions: I. Some boys are intelligent. II. All boys are intelligent.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Some pens are blue</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>No pen is blue</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>All blue are pencils</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>No conclusion</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>No connection between pen and blue</t>
+          <t>No definite relation proven across categories.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>No table is chair. All chairs are wooden. Conclusion?</t>
+          <t>Some buses are cars. All cars are vehicles. Conclusions: I. Some buses are vehicles. II. All vehicles are buses.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Some tables are wooden</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>No table is wooden</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>No chair is table</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>No chair is table</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>No table → chair = No chair → table</t>
+          <t>Transitive link holds.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Some pens are pencils. All pencils are erasers. Conclusions: I. Some pens are erasers. II. All erasers are pencils.</t>
+          <t>All mangoes are fruits. No fruit is vegetable. Conclusion?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some mangoes are vegetables</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All mangoes are vegetables</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>No mango is vegetable</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No mango is vegetable</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Some pens overlap with erasers due to common pencils.</t>
+          <t>All mangoes → fruits, and no fruit → vegetable</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>No lion is a deer. Some deer are animals. Conclusion?</t>
+          <t>All kids are students. No student is teacher. Conclusions: I. No kid is teacher. II. Some teachers are students.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No lion is an animal</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Some lions are deer</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>No deer is lion</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>No deer is lion</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>No lion → deer = No deer → lion</t>
+          <t>Exclusion travels to subgroup.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>Some P are Q. No Q is R. Are some P not R?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3981,37 +3981,37 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Since no Q is R, some P may not be R.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>All stars are hot. Some hot things are bright. Conclusion?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>All stars are bright</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Some stars are bright</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Some stars are hot</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4021,77 +4021,77 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Some stars are hot</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>All stars → hot</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Some keys are locks. Some locks are doors. Conclusions: I. Some keys are doors. II. All keys are doors.</t>
+          <t>No M is N. All N are O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>No definite connection between keys and doors.</t>
+          <t>No conclusive info.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>All lions are animals. Some animals are wild. Are all lions wild?</t>
+          <t>Some toys are plastic. All plastic is harmful. Conclusion?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some toys are harmful</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All toys are harmful</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some harmful are toys</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4101,22 +4101,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some toys are harmful</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Only some animals are wild.</t>
+          <t>Some toys → plastic → harmful</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>No H is I, so some F not I.</t>
+          <t>Because some Z not X, some Y not X.</t>
         </is>
       </c>
     </row>
@@ -4156,47 +4156,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>All cars are vehicles. All trucks are vehicles. Conclusions: I. Some trucks are cars. II. All cars are trucks.</t>
+          <t>All apples are fruits. Some fruits are sweet. What follows?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Some apples are sweet</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All sweet are fruits</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some fruits are apples</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>All apples are sweet</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Some fruits are apples</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Common class doesn’t mean crossover between groups.</t>
+          <t>All apples → fruits, so some fruits ← apples</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>All pens are tools. Some tools are pencils. Are some pens pencils?</t>
+          <t>All flowers are plants. Some plants are medicinal. Are all flowers medicinal?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No direct relation between pens and pencils.</t>
+          <t>Only some plants are medicinal.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Some cups are plates. All plates are spoons. Conclusions: I. Some cups are spoons. II. All spoons are cups.</t>
+          <t>All engineers are professionals. Some professionals are teachers. Conclusions: I. Some engineers are teachers. II. All engineers are teachers.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4261,22 +4261,22 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Some indirect overlap is inferred.</t>
+          <t>Overlap can’t be assumed.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>All rivers are water bodies. Some water bodies are dirty. Are some rivers dirty?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4301,62 +4301,62 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>No V is W, so some T are not W.</t>
+          <t>No direct info on rivers and dirty.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>All pens are pencils. No pencil is marker. Conclusions: I. No pen is marker. II. Some markers are pens.</t>
+          <t>Some engineers are scientists. No scientist is artist. Are some engineers not artists?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Transitive exclusion applies.</t>
+          <t>Engineers partly overlap scientists; scientists exclude artists.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Some teachers are strict. All strict people are effective. Are some teachers effective?</t>
+          <t>All cars are vehicles. Some vehicles are fast. Are all cars fast?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4381,117 +4381,117 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Some teachers are strict and strict people are effective.</t>
+          <t>Only some vehicles are fast, no info about cars.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Some M are N. No N is O. All O are P. Are some M not P?</t>
+          <t>Some birds are parrots. Some parrots are green. Conclusions: I. Some birds are green. II. Some green are parrots.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Insufficient data.</t>
+          <t>Direct overlap of some parrots and green.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>All flowers are plants. Some plants are green. Conclusions: I. All flowers are green. II. Some flowers are green.</t>
+          <t>No tree is stone. Some stones are heavy. Conclusion?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>No tree is heavy</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Some trees are heavy</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>All stones are trees</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Cannot determine specific intersection from partial.</t>
+          <t>No connection between tree and heavy</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>All mangoes are fruits. No fruit is vegetable. Conclusion?</t>
+          <t>No table is chair. All chairs are wooden. Conclusion?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Some mangoes are vegetables</t>
+          <t>Some tables are wooden</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>All mangoes are vegetables</t>
+          <t>No table is wooden</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>No mango is vegetable</t>
+          <t>No chair is table</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4501,117 +4501,117 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>No mango is vegetable</t>
+          <t>No chair is table</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>All mangoes → fruits, and no fruit → vegetable</t>
+          <t>No table → chair = No chair → table</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>Some mangoes are sweet. All sweet things are healthy. Conclusions: I. Some mangoes are healthy. II. All mangoes are healthy.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Indirect conclusion from overlap.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>No flowers are trees. Some trees are plants. Are some flowers plants?</t>
+          <t>Some boys are singers. All singers are dancers. Conclusions: I. Some boys are dancers. II. All dancers are boys.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>No direct relation given between flowers and plants.</t>
+          <t>Some boys overlap dancers via singers.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>No cats are dogs. All dogs are animals. Are no cats animals?</t>
+          <t>Some pencils are long. All long things are thin. Conclusion?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some pencils are thin</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All pencils are thin</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some thin things are pencils</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4621,62 +4621,62 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some pencils are thin</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>No info on cats and animals.</t>
+          <t>Some pencils → long → thin</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>All lions are wild. No wild is pet. Conclusions: I. No lion is pet. II. Some lions are pets.</t>
+          <t>No D is E. Some F are D. All F are G. Are some G not E?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Categorical exclusion carries to subset.</t>
+          <t>Since no D is E and some F are D, some G (which include F) are not E.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4701,37 +4701,37 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>No V is W, so some T not W.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Some books are novels. All novels are fiction. Conclusion?</t>
+          <t>All J are K. Some K are L. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Some books are fiction</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>All books are fiction</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>All fiction are novels</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4741,102 +4741,102 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Some books are fiction</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Some books → novels → fiction</t>
+          <t>Since no L is M, some J not M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Some birds are flying creatures. All flying creatures can fly. Can some birds fly?</t>
+          <t>All squares are rectangles. All rectangles are shapes. Conclusions: I. All squares are shapes. II. Some shapes are squares.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Some birds belong to flying creatures which can fly.</t>
+          <t>Multiple logical links proven.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>All goats are mammals. All mammals are animals. Conclusions: I. All goats are animals. II. All animals are goats.</t>
+          <t>Some teachers are strict. All strict people are effective. Are some teachers effective?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Proper direction of deduction matters.</t>
+          <t>Some teachers are strict and strict people are effective.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>No cars are bikes. All bikes are fast. Are no cars fast?</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>No info on cars and fast relation.</t>
+          <t>Because some Z not X, some Y not X.</t>
         </is>
       </c>
     </row>
@@ -4876,22 +4876,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>No fish is bird. All birds can fly. Conclusion?</t>
+          <t>No A is B. Some B are C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No fish can fly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>All fish are birds</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Some fish can fly</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4901,22 +4901,22 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>No fish can fly</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>No fish → bird → fly</t>
+          <t>No conclusive data.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>No pencils are erasers. All erasers are stationery. Are no pencils stationery?</t>
+          <t>All birds can fly. Some birds are colorful. Are some colorful things flying?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4946,17 +4946,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>No info on pencils and stationery relation.</t>
+          <t>No direct info on colorful things and flying.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4981,22 +4981,22 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>No R is S, so some P not S.</t>
+          <t>No direct conclusion can be drawn about A and D.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>All cars are vehicles. Some vehicles are expensive. Are all cars expensive?</t>
+          <t>No doctors are lawyers. Some lawyers are teachers. Are some doctors teachers?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5026,17 +5026,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Some vehicles are expensive, cars may or may not be expensive.</t>
+          <t>No direct relation between doctors and teachers.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>No A is B. All B are C. Some C are D. Are some A not D?</t>
+          <t>Some fruits are sweet. All sweets are tasty. Are some fruits tasty?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5061,182 +5061,182 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>No direct link between A and D.</t>
+          <t>Some fruits are sweet and sweets are tasty.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All goats are mammals. All mammals are animals. Conclusions: I. All goats are animals. II. All animals are goats.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Because some Z are not X, and some Y are Z, some Y may not be X.</t>
+          <t>Proper direction of deduction matters.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>No X is Y. All Y are Z. Are some Z not X?</t>
+          <t>Some mobiles are gadgets. All gadgets are expensive. Conclusions: I. Some mobiles are expensive. II. All mobiles are gadgets.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Since no X is Y and all Y are Z, some Z are not X.</t>
+          <t>Indirect connection possible for subset.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
+          <t>Some dogs are cats. No cat is rabbit. Conclusions: I. Some dogs are rabbits. II. No dog is rabbit.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>No direct link.</t>
+          <t>Insufficient link between groups.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
+          <t>No bird is insect. All parrots are birds. Conclusions: I. No parrot is insect. II. Some insects are birds.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>No R is S, so some P not S.</t>
+          <t>Parrot subset inherits bird restriction.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>No S is T. Some T are U. All U are V. Are some S not V?</t>
+          <t>Some boys are tall. All tall people are strong. Are some boys strong?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5266,97 +5266,97 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>No S is T, so some S not V.</t>
+          <t>Some boys are tall and tall people are strong.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Some fruits are mangoes. All mangoes are yellow. Conclusions: I. Some fruits are yellow. II. All fruits are mangoes.</t>
+          <t>Some P are Q. No Q is R. Are some P not R?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Through mangoes, yellow connection inferred.</t>
+          <t>No Q is R, so some P not R.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>No bird is insect. All parrots are birds. Conclusions: I. No parrot is insect. II. Some insects are birds.</t>
+          <t>No flowers are trees. Some trees are plants. Are some flowers plants?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Parrot subset inherits bird restriction.</t>
+          <t>No direct relation given between flowers and plants.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>All rivers are water bodies. Some water bodies are dirty. Are some rivers dirty?</t>
+          <t>No birds are mammals. All mammals breathe air. Are no birds breathe air?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5386,72 +5386,72 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>No direct info on rivers and dirty.</t>
+          <t>No info on birds and breathing.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>No dogs are cats. All cats are animals. Are no dogs animals?</t>
+          <t>All boys are students. Some students are girls. Conclusions: I. Some boys are girls. II. All girls are students.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>We cannot conclude about dogs being animals.</t>
+          <t>Some students are girls, so some girls are students.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Some cars are fast. All fast things are expensive. Are some cars expensive?</t>
+          <t>No lion is a deer. Some deer are animals. Conclusion?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No lion is an animal</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some lions are deer</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>No deer is lion</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5461,62 +5461,62 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No deer is lion</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Some cars are fast and fast things are expensive.</t>
+          <t>No lion → deer = No deer → lion</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>All cows are animals. All animals are herbivores. Conclusions: I. Some cows are herbivores. II. All cows are herbivores.</t>
+          <t>All P are Q. Some Q are R. No R is S. Are some P not S?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Cows ⊂ animals ⊂ herbivores.</t>
+          <t>No R is S, so some P not S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>No bats are birds. All birds can fly. Are no bats able to fly?</t>
+          <t>Some flowers are red. All red things are attractive. Are some flowers attractive?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5541,102 +5541,102 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>No info on bats' flying ability here.</t>
+          <t>Some flowers are red and red things are attractive.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>No train is plane. All planes are fast. Conclusions: I. No train is fast. II. Some fast are planes.</t>
+          <t>Some birds are flying creatures. All flying creatures can fly. Can some birds fly?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Statement I overextends logic.</t>
+          <t>Some birds belong to flying creatures which can fly.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>All boys are students. Some students are girls. Conclusions: I. Some boys are girls. II. All girls are students.</t>
+          <t>Some J are K. No K is L. All L are M. Are some J not M?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Some students are girls, so some girls are students.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>All cars are vehicles. Some vehicles are fast. Are all cars fast?</t>
+          <t>No S is T. Some T are U. All U are V. Are some S not V?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5661,22 +5661,22 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Only some vehicles are fast, no info about cars.</t>
+          <t>No S is T, so some S not V.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
+          <t>Some students are intelligent. All intelligent people succeed. Do some students succeed?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5701,117 +5701,117 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Some students are intelligent who succeed.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>No cars are bicycles. Some bicycles are two-wheelers. Are no cars two-wheelers?</t>
+          <t>All lions are animals. No animal is plant. Conclusions: I. No lion is plant. II. All lions are plants.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>No info on cars and two-wheelers.</t>
+          <t>Lions ⊂ animals, animals ≠ plants.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Some boys are singers. All singers are dancers. Conclusions: I. Some boys are dancers. II. All dancers are boys.</t>
+          <t>No dogs are cats. All cats are pets. Are no dogs pets?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Some boys overlap dancers via singers.</t>
+          <t>No info on dogs and pets.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>No fish are birds. All birds have wings. Are no fish have wings?</t>
+          <t>Some boys are students. All students are intelligent. What follows?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>All boys are intelligent</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Some boys are intelligent</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>All intelligent are students</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5821,62 +5821,62 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some boys are intelligent</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>No info on fish and wings.</t>
+          <t>Some boys → students → intelligent</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Some doctors are rich. All rich people are happy. Are some doctors happy?</t>
+          <t>All fruits are healthy. Some healthy are tasty. Conclusion?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some fruits are tasty</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All healthy are fruits</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some fruits are healthy</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>All tasty are fruits</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some fruits are healthy</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Some doctors are rich and rich people are happy.</t>
+          <t>All fruits → healthy</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are living beings. Are all cats living beings?</t>
+          <t>Some A are B. All B are C. Some C are not D. Are some A not D?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5901,62 +5901,62 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>If all cats are animals and all animals are living beings, all cats are living beings.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>All paper is white. Some white is light. Conclusions: I. Some paper is light. II. All light is white.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>No V is W, so some T not W.</t>
+          <t>No guaranteed overlap shown.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>No books are newspapers. Some newspapers are daily. Are no books daily?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>No conclusive relation between M and P.</t>
+          <t>No info on books being daily.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Some birds are parrots. All parrots are green. What can we say?</t>
+          <t>No cats are dogs. All dogs are animals. Are no cats animals?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Some birds are green</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>All green are parrots</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Some parrots are birds</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6021,62 +6021,62 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Some parrots are birds</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Some birds → parrots</t>
+          <t>No info on cats and animals.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Some mobiles are gadgets. All gadgets are expensive. Conclusions: I. Some mobiles are expensive. II. All mobiles are gadgets.</t>
+          <t>All apples are fruits. Some fruits are sour. Are some apples sour?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Indirect connection possible for subset.</t>
+          <t>No info on apples being sour.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>No cats are mice. All mice are small. Are no cats small?</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6101,62 +6101,62 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>No info on cats and small.</t>
+          <t>Since no V is W, some T which are U and U are V, are not W.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>All roses are red. Some red things are beautiful. Conclusions: I. Some roses are beautiful. II. All red things are roses.</t>
+          <t>All dogs are animals. All animals are living beings. What can we conclude?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>All dogs are living beings</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>All living beings are dogs</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Some animals are not dogs</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>No conclusion</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>All dogs are living beings</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Common trait not confirmed for subset.</t>
+          <t>A → B → C means A → C</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>No birds are mammals. All mammals breathe air. Are no birds breathe air?</t>
+          <t>No cars are bikes. All bikes are fast. Are no cars fast?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6186,57 +6186,57 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>No info on birds and breathing.</t>
+          <t>No info on cars and fast relation.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Some chairs are wooden. All wooden are brown. Conclusion?</t>
+          <t>No train is plane. All planes are fast. Conclusions: I. No train is fast. II. Some fast are planes.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>All chairs are brown</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Some chairs are brown</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Some wooden are chairs</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Some chairs are brown</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Some chairs → wooden → brown</t>
+          <t>Statement I overextends logic.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>All stones are rocks. Some rocks are heavy. Conclusions: I. Some stones are heavy. II. All heavy are rocks.</t>
+          <t>All pens are pencils. No pencil is marker. Conclusions: I. No pen is marker. II. Some markers are pens.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6261,77 +6261,77 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Overlap is not definite.</t>
+          <t>Transitive exclusion applies.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
+          <t>All dogs are animals. Some animals are cats. Conclusions: I. Some dogs are cats. II. All animals are dogs.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Because some Z not X, some Y not X.</t>
+          <t>Only the conclusions logically follow based on statements.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Some toys are plastic. All plastic is harmful. Conclusion?</t>
+          <t>Some K are L. Some L are M. No M is N. Are some K not N?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Some toys are harmful</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>All toys are harmful</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Some harmful are toys</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6341,62 +6341,62 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Some toys are harmful</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Some toys → plastic → harmful</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Some dogs are cats. No cat is rabbit. Conclusions: I. Some dogs are rabbits. II. No dog is rabbit.</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Insufficient link between groups.</t>
+          <t>No V is W, so some T not W.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
+          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6421,22 +6421,22 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>No direct conclusion can be drawn about A and D.</t>
+          <t>No V is W, so some T are not W.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Some fruits are sweet. All sweets are tasty. Are some fruits tasty?</t>
+          <t>No bats are birds. All birds can fly. Are no bats able to fly?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Some fruits are sweet and sweets are tasty.</t>
+          <t>No info on bats' flying ability here.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Some mangoes are sweet. All sweet things are healthy. Conclusions: I. Some mangoes are healthy. II. All mangoes are healthy.</t>
+          <t>All cows are animals. All animals are herbivores. Conclusions: I. Some cows are herbivores. II. All cows are herbivores.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6501,22 +6501,22 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Indirect conclusion from overlap.</t>
+          <t>Cows ⊂ animals ⊂ herbivores.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>All kids are students. No student is teacher. Conclusions: I. No kid is teacher. II. Some teachers are students.</t>
+          <t>No apple is banana. Some bananas are yellow. Conclusions: I. Some apples are yellow. II. No apple is yellow.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6541,22 +6541,22 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Exclusion travels to subgroup.</t>
+          <t>No definite apple-yellow link.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Some T are U. All U are V. No V is W. Are some T not W?</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6581,22 +6581,22 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Since no V is W, some T which are U and U are V, are not W.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>Some A are B. No B is C. All C are D. Are some A not D?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>No conclusive relation.</t>
+          <t>No direct link.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>All birds can fly. Some birds are colorful. Are some colorful things flying?</t>
+          <t>All pens are tools. Some tools are pencils. Are some pens pencils?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>No direct info on colorful things and flying.</t>
+          <t>No direct relation between pens and pencils.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>No books are newspapers. Some newspapers are daily. Are no books daily?</t>
+          <t>No books are papers. All papers are white. Are no books white?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6706,17 +6706,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>No info on books being daily.</t>
+          <t>No info on books and white.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Some chairs are tables. All tables are wood. Conclusions: I. Some chairs are wood. II. All wood are tables.</t>
+          <t>All cats are animals. All animals are mammals. Conclusions: I. All cats are mammals. II. All mammals are cats.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6736,27 +6736,27 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None follow</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>'Some' does not imply full connection unless supported.</t>
+          <t>All members of first category are also members of the final category.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Some boys are tall. All tall people are strong. Are some boys strong?</t>
+          <t>All cars are vehicles. Some vehicles are expensive. Are all cars expensive?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6781,22 +6781,22 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Some boys are tall and tall people are strong.</t>
+          <t>Some vehicles are expensive, cars may or may not be expensive.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>All apples are fruits. Some fruits are red. Are some apples red?</t>
+          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6826,57 +6826,57 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>No direct info on apples and red.</t>
+          <t>Insufficient data.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>All students are learners. Some learners are athletes. Are some students athletes?</t>
+          <t>Some apples are fruits. All fruits are healthy. Conclusions: I. Some apples are healthy. II. All apples are healthy.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>No direct info on students and athletes.</t>
+          <t>Part of a group being linked to another through common element.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Some K are L. Some L are M. No M is N. Are some K not N?</t>
+          <t>All cats are animals. All animals are living beings. Are all cats living beings?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6901,22 +6901,22 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>If all cats are animals and all animals are living beings, all cats are living beings.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Some P are Q. No Q is R. Are some P not R?</t>
+          <t>Some men are honest. All honest people are respected. Are some men respected?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>No Q is R, so some P not R.</t>
+          <t>Some men are honest and honest people are respected.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>No bird is mammal. All mammals are warm-blooded. Conclusions: I. No bird is warm-blooded. II. Some warm-blooded are mammals.</t>
+          <t>All kings are rulers. No ruler is weak. Conclusions: I. No king is weak. II. All weak are kings.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>All mammals ⊂ warm-blooded, so II true.</t>
+          <t>Exclusive trait of group extends to all members.</t>
         </is>
       </c>
     </row>
@@ -6996,22 +6996,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Some cats are black. All black are wild. Conclusion?</t>
+          <t>All J are K. Some L are K. No L is M. Are some J not M?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Some cats are wild</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>All cats are wild</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Some black are cats</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7021,37 +7021,37 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Some cats are wild</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Some cats → black → wild</t>
+          <t>Since no L is M and some L are K, some J may not be M.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>All flowers are beautiful. Some beautiful things are expensive. Are some flowers expensive?</t>
+          <t>All pens are objects. Some objects are useful. Conclusion?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some pens are useful</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All useful are pens</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some objects are pens</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7061,142 +7061,142 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Some objects are pens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>No direct info about flowers and expensive.</t>
+          <t>All pens → objects</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Some cars are red. All red things are bright. Are some cars bright?</t>
+          <t>All flowers are plants. Some plants are green. Conclusions: I. All flowers are green. II. Some flowers are green.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Some cars are red and red things are bright.</t>
+          <t>Cannot determine specific intersection from partial.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>No apple is orange. All oranges are juicy. Conclusion?</t>
+          <t>Some tables are chairs. No chair is sofa. Conclusions: I. Some tables are not sofas. II. No table is sofa.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>No apple is juicy</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Some apples are juicy</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>All apples are oranges</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>No link between apple and juicy</t>
+          <t>We know chairs ≠ sofa; table partially overlaps.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>All M are N. No N is O. Some O are P. Are some M not P?</t>
+          <t>All roses are red. Some red things are beautiful. Conclusions: I. Some roses are beautiful. II. All red things are roses.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Insufficient info.</t>
+          <t>Common trait not confirmed for subset.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>No M is N. Some N are O. All O are P. Are some M not P?</t>
+          <t>Some cars are red. All red things are bright. Are some cars bright?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7221,102 +7221,102 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>No conclusive data.</t>
+          <t>Some cars are red and red things are bright.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>All cats are animals. All animals are living beings. Conclusions: I. Some cats are living beings. II. All living beings are cats.</t>
+          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Cats ⊂ animals ⊂ living beings.</t>
+          <t>Because no H is I, some F not I.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Some books are pens. Some pens are colors. Conclusions: I. Some books are colors. II. All colors are pens.</t>
+          <t>All lions are animals. Some animals are wild. Are all lions wild?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Indirect link not confirmed.</t>
+          <t>Only some animals are wild.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>All dogs are animals. Some animals are cats. Conclusions: I. Some dogs are cats. II. All animals are dogs.</t>
+          <t>Some chairs are tables. All tables are wood. Conclusions: I. Some chairs are wood. II. All wood are tables.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7346,47 +7346,47 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Only the conclusions logically follow based on statements.</t>
+          <t>'Some' does not imply full connection unless supported.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>All kings are rulers. No ruler is weak. Conclusions: I. No king is weak. II. All weak are kings.</t>
+          <t>No X is Y. Some Y are Z. All Z are W. Are some X not W?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Exclusive trait of group extends to all members.</t>
+          <t>Insufficient info.</t>
         </is>
       </c>
     </row>
@@ -7396,47 +7396,47 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>All squares are rectangles. All rectangles are shapes. Conclusions: I. All squares are shapes. II. Some shapes are squares.</t>
+          <t>All X are Y. Some Y are Z. Some Z are not X. Are some Y not X?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Only I follows</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Only II follows</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Cannot say</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Neither follows</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Both follow</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Multiple logical links proven.</t>
+          <t>Some Z not X implies some Y not X.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>No doctors are lawyers. Some lawyers are teachers. Are some doctors teachers?</t>
+          <t>All F are G. Some G are H. No H is I. Are some F not I?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cannot say</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>No direct relation between doctors and teachers.</t>
+          <t>No H is I, so some F not I.</t>
         </is>
       </c>
     </row>
